--- a/research/traditional_assets/database/data/pakistan/pakistan_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_hotel_gaming.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1681124804964966</v>
+        <v>0.1676569043030567</v>
       </c>
       <c r="C2">
-        <v>141.1595232172767</v>
+        <v>140.3471894023749</v>
       </c>
       <c r="D2">
-        <v>140.0695232172767</v>
+        <v>140.5931894023749</v>
       </c>
       <c r="E2">
-        <v>-40.4</v>
+        <v>-39.064</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.336</v>
       </c>
       <c r="G2">
         <v>1.09</v>
@@ -1576,28 +1576,28 @@
         <v>15.87</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0672008</v>
       </c>
       <c r="N2">
-        <v>15.87</v>
+        <v>15.8027992</v>
       </c>
       <c r="O2">
-        <v>4.6023</v>
+        <v>4.582811767999999</v>
       </c>
       <c r="P2">
-        <v>11.2677</v>
+        <v>11.219987432</v>
       </c>
       <c r="Q2">
-        <v>14.3977</v>
+        <v>14.349987432</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1681124804964966</v>
+        <v>0.1689896710131886</v>
       </c>
       <c r="T2">
-        <v>0.7480479046815168</v>
+        <v>0.7534126926847883</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>236.1579028821085</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1676569043030567</v>
+        <v>0.1672013281096169</v>
       </c>
       <c r="C3">
-        <v>140.3471894023749</v>
+        <v>139.5387858549744</v>
       </c>
       <c r="D3">
-        <v>140.5931894023749</v>
+        <v>141.1207858549744</v>
       </c>
       <c r="E3">
-        <v>-39.064</v>
+        <v>-37.728</v>
       </c>
       <c r="F3">
-        <v>1.336</v>
+        <v>2.672</v>
       </c>
       <c r="G3">
         <v>1.09</v>
@@ -1658,28 +1658,28 @@
         <v>15.87</v>
       </c>
       <c r="M3">
-        <v>0.0672008</v>
+        <v>0.1344016</v>
       </c>
       <c r="N3">
-        <v>15.8027992</v>
+        <v>15.7355984</v>
       </c>
       <c r="O3">
-        <v>4.582811767999999</v>
+        <v>4.563323536</v>
       </c>
       <c r="P3">
-        <v>11.219987432</v>
+        <v>11.172274864</v>
       </c>
       <c r="Q3">
-        <v>14.349987432</v>
+        <v>14.302274864</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1689896710131886</v>
+        <v>0.1698847633771601</v>
       </c>
       <c r="T3">
-        <v>0.7534126926847883</v>
+        <v>0.7588869661575144</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>236.1579028821085</v>
+        <v>118.0789514410543</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1672013281096169</v>
+        <v>0.166745751916177</v>
       </c>
       <c r="C4">
-        <v>139.5387858549744</v>
+        <v>138.7343569884492</v>
       </c>
       <c r="D4">
-        <v>141.1207858549744</v>
+        <v>141.6523569884492</v>
       </c>
       <c r="E4">
-        <v>-37.728</v>
+        <v>-36.392</v>
       </c>
       <c r="F4">
-        <v>2.672</v>
+        <v>4.008</v>
       </c>
       <c r="G4">
         <v>1.09</v>
@@ -1740,28 +1740,28 @@
         <v>15.87</v>
       </c>
       <c r="M4">
-        <v>0.1344016</v>
+        <v>0.2016024</v>
       </c>
       <c r="N4">
-        <v>15.7355984</v>
+        <v>15.6683976</v>
       </c>
       <c r="O4">
-        <v>4.563323536</v>
+        <v>4.543835303999999</v>
       </c>
       <c r="P4">
-        <v>11.172274864</v>
+        <v>11.124562296</v>
       </c>
       <c r="Q4">
-        <v>14.302274864</v>
+        <v>14.254562296</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1698847633771601</v>
+        <v>0.1707983112537908</v>
       </c>
       <c r="T4">
-        <v>0.7588869661575144</v>
+        <v>0.7644741112482347</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>118.0789514410543</v>
+        <v>78.71930096070285</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.166745751916177</v>
+        <v>0.1662901757227372</v>
       </c>
       <c r="C5">
-        <v>138.7343569884492</v>
+        <v>137.9339478878855</v>
       </c>
       <c r="D5">
-        <v>141.6523569884492</v>
+        <v>142.1879478878855</v>
       </c>
       <c r="E5">
-        <v>-36.392</v>
+        <v>-35.056</v>
       </c>
       <c r="F5">
-        <v>4.008</v>
+        <v>5.344</v>
       </c>
       <c r="G5">
         <v>1.09</v>
@@ -1822,28 +1822,28 @@
         <v>15.87</v>
       </c>
       <c r="M5">
-        <v>0.2016024</v>
+        <v>0.2688032</v>
       </c>
       <c r="N5">
-        <v>15.6683976</v>
+        <v>15.6011968</v>
       </c>
       <c r="O5">
-        <v>4.543835303999999</v>
+        <v>4.524347071999999</v>
       </c>
       <c r="P5">
-        <v>11.124562296</v>
+        <v>11.076849728</v>
       </c>
       <c r="Q5">
-        <v>14.254562296</v>
+        <v>14.206849728</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1707983112537908</v>
+        <v>0.1717308913778513</v>
       </c>
       <c r="T5">
-        <v>0.7644741112482347</v>
+        <v>0.7701776551950117</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>78.71930096070285</v>
+        <v>59.03947572052713</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1662901757227372</v>
+        <v>0.1658345995292974</v>
       </c>
       <c r="C6">
-        <v>137.9339478878855</v>
+        <v>137.1376043228284</v>
       </c>
       <c r="D6">
-        <v>142.1879478878855</v>
+        <v>142.7276043228284</v>
       </c>
       <c r="E6">
-        <v>-35.056</v>
+        <v>-33.72</v>
       </c>
       <c r="F6">
-        <v>5.344</v>
+        <v>6.68</v>
       </c>
       <c r="G6">
         <v>1.09</v>
@@ -1904,28 +1904,28 @@
         <v>15.87</v>
       </c>
       <c r="M6">
-        <v>0.2688032</v>
+        <v>0.336004</v>
       </c>
       <c r="N6">
-        <v>15.6011968</v>
+        <v>15.533996</v>
       </c>
       <c r="O6">
-        <v>4.524347071999999</v>
+        <v>4.504858839999999</v>
       </c>
       <c r="P6">
-        <v>11.076849728</v>
+        <v>11.02913716</v>
       </c>
       <c r="Q6">
-        <v>14.206849728</v>
+        <v>14.15913716</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1717308913778513</v>
+        <v>0.1726831047676815</v>
       </c>
       <c r="T6">
-        <v>0.7701776551950117</v>
+        <v>0.7760012737511945</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>59.03947572052713</v>
+        <v>47.23158057642171</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1658345995292974</v>
+        <v>0.1653790233358576</v>
       </c>
       <c r="C7">
-        <v>137.1376043228284</v>
+        <v>136.3453727603206</v>
       </c>
       <c r="D7">
-        <v>142.7276043228284</v>
+        <v>143.2713727603206</v>
       </c>
       <c r="E7">
-        <v>-33.72</v>
+        <v>-32.384</v>
       </c>
       <c r="F7">
-        <v>6.68</v>
+        <v>8.016</v>
       </c>
       <c r="G7">
         <v>1.09</v>
@@ -1986,28 +1986,28 @@
         <v>15.87</v>
       </c>
       <c r="M7">
-        <v>0.336004</v>
+        <v>0.4032048</v>
       </c>
       <c r="N7">
-        <v>15.533996</v>
+        <v>15.4667952</v>
       </c>
       <c r="O7">
-        <v>4.504858839999999</v>
+        <v>4.485370607999999</v>
       </c>
       <c r="P7">
-        <v>11.02913716</v>
+        <v>10.981424592</v>
       </c>
       <c r="Q7">
-        <v>14.15913716</v>
+        <v>14.111424592</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1726831047676815</v>
+        <v>0.1736555780168697</v>
       </c>
       <c r="T7">
-        <v>0.7760012737511945</v>
+        <v>0.7819487990851686</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>47.23158057642171</v>
+        <v>39.35965048035143</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1653790233358576</v>
+        <v>0.1649234471424177</v>
       </c>
       <c r="C8">
-        <v>136.3453727603206</v>
+        <v>135.5573003782396</v>
       </c>
       <c r="D8">
-        <v>143.2713727603206</v>
+        <v>143.8193003782396</v>
       </c>
       <c r="E8">
-        <v>-32.384</v>
+        <v>-31.048</v>
       </c>
       <c r="F8">
-        <v>8.016</v>
+        <v>9.351999999999999</v>
       </c>
       <c r="G8">
         <v>1.09</v>
@@ -2068,28 +2068,28 @@
         <v>15.87</v>
       </c>
       <c r="M8">
-        <v>0.4032048</v>
+        <v>0.4704055999999999</v>
       </c>
       <c r="N8">
-        <v>15.4667952</v>
+        <v>15.3995944</v>
       </c>
       <c r="O8">
-        <v>4.485370607999999</v>
+        <v>4.465882376</v>
       </c>
       <c r="P8">
-        <v>10.981424592</v>
+        <v>10.933712024</v>
       </c>
       <c r="Q8">
-        <v>14.111424592</v>
+        <v>14.063712024</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1736555780168697</v>
+        <v>0.1746489646692664</v>
       </c>
       <c r="T8">
-        <v>0.7819487990851686</v>
+        <v>0.7880242281897657</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>39.35965048035143</v>
+        <v>33.73684326887265</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1649234471424177</v>
+        <v>0.1644678709489779</v>
       </c>
       <c r="C9">
-        <v>135.5573003782396</v>
+        <v>134.7734350789429</v>
       </c>
       <c r="D9">
-        <v>143.8193003782396</v>
+        <v>144.3714350789429</v>
       </c>
       <c r="E9">
-        <v>-31.048</v>
+        <v>-29.712</v>
       </c>
       <c r="F9">
-        <v>9.352</v>
+        <v>10.688</v>
       </c>
       <c r="G9">
         <v>1.09</v>
@@ -2150,28 +2150,28 @@
         <v>15.87</v>
       </c>
       <c r="M9">
-        <v>0.4704056</v>
+        <v>0.5376064</v>
       </c>
       <c r="N9">
-        <v>15.3995944</v>
+        <v>15.3323936</v>
       </c>
       <c r="O9">
-        <v>4.465882376</v>
+        <v>4.446394143999999</v>
       </c>
       <c r="P9">
-        <v>10.933712024</v>
+        <v>10.885999456</v>
       </c>
       <c r="Q9">
-        <v>14.063712024</v>
+        <v>14.015999456</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1746489646692664</v>
+        <v>0.1756639466836716</v>
       </c>
       <c r="T9">
-        <v>0.7880242281897657</v>
+        <v>0.7942317318401148</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.73684326887265</v>
+        <v>29.51973786026356</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1644678709489779</v>
+        <v>0.164012294755538</v>
       </c>
       <c r="C10">
-        <v>134.7734350789429</v>
+        <v>133.9938255032276</v>
       </c>
       <c r="D10">
-        <v>144.3714350789429</v>
+        <v>144.9278255032276</v>
       </c>
       <c r="E10">
-        <v>-29.712</v>
+        <v>-28.376</v>
       </c>
       <c r="F10">
-        <v>10.688</v>
+        <v>12.024</v>
       </c>
       <c r="G10">
         <v>1.09</v>
@@ -2232,28 +2232,28 @@
         <v>15.87</v>
       </c>
       <c r="M10">
-        <v>0.5376064</v>
+        <v>0.6048071999999999</v>
       </c>
       <c r="N10">
-        <v>15.3323936</v>
+        <v>15.2651928</v>
       </c>
       <c r="O10">
-        <v>4.446394143999999</v>
+        <v>4.426905912</v>
       </c>
       <c r="P10">
-        <v>10.885999456</v>
+        <v>10.838286888</v>
       </c>
       <c r="Q10">
-        <v>14.015999456</v>
+        <v>13.968286888</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1756639466836716</v>
+        <v>0.1767012359950967</v>
       </c>
       <c r="T10">
-        <v>0.7942317318401148</v>
+        <v>0.80057566414212</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.51973786026356</v>
+        <v>26.23976698690095</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.164012294755538</v>
+        <v>0.1635567185620982</v>
       </c>
       <c r="C11">
-        <v>133.9938255032276</v>
+        <v>133.2185210446159</v>
       </c>
       <c r="D11">
-        <v>144.9278255032276</v>
+        <v>145.4885210446159</v>
       </c>
       <c r="E11">
-        <v>-28.376</v>
+        <v>-27.04</v>
       </c>
       <c r="F11">
-        <v>12.024</v>
+        <v>13.36</v>
       </c>
       <c r="G11">
         <v>1.09</v>
@@ -2314,28 +2314,28 @@
         <v>15.87</v>
       </c>
       <c r="M11">
-        <v>0.6048071999999999</v>
+        <v>0.6720079999999998</v>
       </c>
       <c r="N11">
-        <v>15.2651928</v>
+        <v>15.197992</v>
       </c>
       <c r="O11">
-        <v>4.426905912</v>
+        <v>4.407417679999999</v>
       </c>
       <c r="P11">
-        <v>10.838286888</v>
+        <v>10.79057432</v>
       </c>
       <c r="Q11">
-        <v>13.968286888</v>
+        <v>13.92057432</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1767012359950967</v>
+        <v>0.1777615761801091</v>
       </c>
       <c r="T11">
-        <v>0.80057566414212</v>
+        <v>0.8070605727175031</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.23976698690095</v>
+        <v>23.61579028821086</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1635567185620982</v>
+        <v>0.1631011423686584</v>
       </c>
       <c r="C12">
-        <v>133.2185210446158</v>
+        <v>132.4475718639709</v>
       </c>
       <c r="D12">
-        <v>145.4885210446159</v>
+        <v>146.0535718639709</v>
       </c>
       <c r="E12">
-        <v>-27.04</v>
+        <v>-25.704</v>
       </c>
       <c r="F12">
-        <v>13.36</v>
+        <v>14.696</v>
       </c>
       <c r="G12">
         <v>1.09</v>
@@ -2396,28 +2396,28 @@
         <v>15.87</v>
       </c>
       <c r="M12">
-        <v>0.6720079999999999</v>
+        <v>0.7392088</v>
       </c>
       <c r="N12">
-        <v>15.197992</v>
+        <v>15.1307912</v>
       </c>
       <c r="O12">
-        <v>4.407417679999999</v>
+        <v>4.387929448</v>
       </c>
       <c r="P12">
-        <v>10.79057432</v>
+        <v>10.742861752</v>
       </c>
       <c r="Q12">
-        <v>13.92057432</v>
+        <v>13.872861752</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1777615761801091</v>
+        <v>0.1788457442344476</v>
       </c>
       <c r="T12">
-        <v>0.8070605727175031</v>
+        <v>0.8136912095754791</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.61579028821086</v>
+        <v>21.46890026200987</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1631011423686584</v>
+        <v>0.1626455661752185</v>
       </c>
       <c r="C13">
-        <v>132.4475718639709</v>
+        <v>131.6810289044572</v>
       </c>
       <c r="D13">
-        <v>146.0535718639709</v>
+        <v>146.6230289044572</v>
       </c>
       <c r="E13">
-        <v>-25.704</v>
+        <v>-24.368</v>
       </c>
       <c r="F13">
-        <v>14.696</v>
+        <v>16.032</v>
       </c>
       <c r="G13">
         <v>1.09</v>
@@ -2478,28 +2478,28 @@
         <v>15.87</v>
       </c>
       <c r="M13">
-        <v>0.7392088</v>
+        <v>0.8064095999999999</v>
       </c>
       <c r="N13">
-        <v>15.1307912</v>
+        <v>15.0635904</v>
       </c>
       <c r="O13">
-        <v>4.387929448</v>
+        <v>4.368441215999999</v>
       </c>
       <c r="P13">
-        <v>10.742861752</v>
+        <v>10.695149184</v>
       </c>
       <c r="Q13">
-        <v>13.872861752</v>
+        <v>13.825149184</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1788457442344476</v>
+        <v>0.1799545524718392</v>
       </c>
       <c r="T13">
-        <v>0.8136912095754791</v>
+        <v>0.8204725427256818</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.46890026200987</v>
+        <v>19.67982524017571</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1626455661752185</v>
+        <v>0.1621899899817787</v>
       </c>
       <c r="C14">
-        <v>131.6810289044572</v>
+        <v>130.9189439068502</v>
       </c>
       <c r="D14">
-        <v>146.6230289044572</v>
+        <v>147.1969439068502</v>
       </c>
       <c r="E14">
-        <v>-24.368</v>
+        <v>-23.032</v>
       </c>
       <c r="F14">
-        <v>16.032</v>
+        <v>17.368</v>
       </c>
       <c r="G14">
         <v>1.09</v>
@@ -2560,28 +2560,28 @@
         <v>15.87</v>
       </c>
       <c r="M14">
-        <v>0.8064095999999999</v>
+        <v>0.8736103999999999</v>
       </c>
       <c r="N14">
-        <v>15.0635904</v>
+        <v>14.9963896</v>
       </c>
       <c r="O14">
-        <v>4.368441215999999</v>
+        <v>4.348952983999999</v>
       </c>
       <c r="P14">
-        <v>10.695149184</v>
+        <v>10.647436616</v>
       </c>
       <c r="Q14">
-        <v>13.825149184</v>
+        <v>13.777436616</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1799545524718392</v>
+        <v>0.1810888505537686</v>
       </c>
       <c r="T14">
-        <v>0.8204725427256818</v>
+        <v>0.8274097685919812</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.67982524017571</v>
+        <v>18.16599252939297</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1621899899817787</v>
+        <v>0.1617344137883388</v>
       </c>
       <c r="C15">
-        <v>130.9189439068502</v>
+        <v>130.1613694252082</v>
       </c>
       <c r="D15">
-        <v>147.1969439068502</v>
+        <v>147.7753694252083</v>
       </c>
       <c r="E15">
-        <v>-23.032</v>
+        <v>-21.696</v>
       </c>
       <c r="F15">
-        <v>17.368</v>
+        <v>18.704</v>
       </c>
       <c r="G15">
         <v>1.09</v>
@@ -2642,28 +2642,28 @@
         <v>15.87</v>
       </c>
       <c r="M15">
-        <v>0.8736103999999999</v>
+        <v>0.9408112</v>
       </c>
       <c r="N15">
-        <v>14.9963896</v>
+        <v>14.9291888</v>
       </c>
       <c r="O15">
-        <v>4.348952983999999</v>
+        <v>4.329464751999999</v>
       </c>
       <c r="P15">
-        <v>10.647436616</v>
+        <v>10.599724048</v>
       </c>
       <c r="Q15">
-        <v>13.777436616</v>
+        <v>13.729724048</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1810888505537686</v>
+        <v>0.1822495276608591</v>
       </c>
       <c r="T15">
-        <v>0.8274097685919812</v>
+        <v>0.8345083252923805</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.16599252939297</v>
+        <v>16.86842163443632</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1617344137883388</v>
+        <v>0.1612788375948989</v>
       </c>
       <c r="C16">
-        <v>130.1613694252082</v>
+        <v>129.408358842915</v>
       </c>
       <c r="D16">
-        <v>147.7753694252083</v>
+        <v>148.358358842915</v>
       </c>
       <c r="E16">
-        <v>-21.696</v>
+        <v>-20.36</v>
       </c>
       <c r="F16">
-        <v>18.704</v>
+        <v>20.04</v>
       </c>
       <c r="G16">
         <v>1.09</v>
@@ -2724,28 +2724,28 @@
         <v>15.87</v>
       </c>
       <c r="M16">
-        <v>0.9408112</v>
+        <v>1.008012</v>
       </c>
       <c r="N16">
-        <v>14.9291888</v>
+        <v>14.861988</v>
       </c>
       <c r="O16">
-        <v>4.329464751999999</v>
+        <v>4.309976519999999</v>
       </c>
       <c r="P16">
-        <v>10.599724048</v>
+        <v>10.55201148</v>
       </c>
       <c r="Q16">
-        <v>13.729724048</v>
+        <v>13.68201148</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1822495276608591</v>
+        <v>0.1834375148175282</v>
       </c>
       <c r="T16">
-        <v>0.8345083252923805</v>
+        <v>0.8417739068563186</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.86842163443632</v>
+        <v>15.74386019214057</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1612788375948989</v>
+        <v>0.1608232614014591</v>
       </c>
       <c r="C17">
-        <v>129.408358842915</v>
+        <v>128.6599663891028</v>
       </c>
       <c r="D17">
-        <v>148.358358842915</v>
+        <v>148.9459663891028</v>
       </c>
       <c r="E17">
-        <v>-20.36</v>
+        <v>-19.024</v>
       </c>
       <c r="F17">
-        <v>20.04</v>
+        <v>21.376</v>
       </c>
       <c r="G17">
         <v>1.09</v>
@@ -2806,28 +2806,28 @@
         <v>15.87</v>
       </c>
       <c r="M17">
-        <v>1.008012</v>
+        <v>1.0752128</v>
       </c>
       <c r="N17">
-        <v>14.861988</v>
+        <v>14.7947872</v>
       </c>
       <c r="O17">
-        <v>4.30997652</v>
+        <v>4.290488287999999</v>
       </c>
       <c r="P17">
-        <v>10.55201148</v>
+        <v>10.504298912</v>
       </c>
       <c r="Q17">
-        <v>13.68201148</v>
+        <v>13.634298912</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1834375148175282</v>
+        <v>0.1846537873826894</v>
       </c>
       <c r="T17">
-        <v>0.8417739068563186</v>
+        <v>0.8492124784574934</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.74386019214057</v>
+        <v>14.75986893013178</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1608232614014591</v>
+        <v>0.1603676852080193</v>
       </c>
       <c r="C18">
-        <v>128.6599663891028</v>
+        <v>127.9162471554687</v>
       </c>
       <c r="D18">
-        <v>148.9459663891028</v>
+        <v>149.5382471554687</v>
       </c>
       <c r="E18">
-        <v>-19.024</v>
+        <v>-17.688</v>
       </c>
       <c r="F18">
-        <v>21.376</v>
+        <v>22.712</v>
       </c>
       <c r="G18">
         <v>1.09</v>
@@ -2888,28 +2888,28 @@
         <v>15.87</v>
       </c>
       <c r="M18">
-        <v>1.0752128</v>
+        <v>1.1424136</v>
       </c>
       <c r="N18">
-        <v>14.7947872</v>
+        <v>14.7275864</v>
       </c>
       <c r="O18">
-        <v>4.290488287999999</v>
+        <v>4.271000056</v>
       </c>
       <c r="P18">
-        <v>10.504298912</v>
+        <v>10.456586344</v>
       </c>
       <c r="Q18">
-        <v>13.634298912</v>
+        <v>13.586586344</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1846537873826894</v>
+        <v>0.1858993677205052</v>
       </c>
       <c r="T18">
-        <v>0.8492124784574934</v>
+        <v>0.8568302927478531</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.75986893013178</v>
+        <v>13.89164134600638</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1603676852080193</v>
+        <v>0.1599121090145794</v>
       </c>
       <c r="C19">
-        <v>127.9162471554687</v>
+        <v>127.1772571134921</v>
       </c>
       <c r="D19">
-        <v>149.5382471554687</v>
+        <v>150.1352571134921</v>
       </c>
       <c r="E19">
-        <v>-17.688</v>
+        <v>-16.352</v>
       </c>
       <c r="F19">
-        <v>22.712</v>
+        <v>24.048</v>
       </c>
       <c r="G19">
         <v>1.09</v>
@@ -2970,28 +2970,28 @@
         <v>15.87</v>
       </c>
       <c r="M19">
-        <v>1.1424136</v>
+        <v>1.2096144</v>
       </c>
       <c r="N19">
-        <v>14.7275864</v>
+        <v>14.6603856</v>
       </c>
       <c r="O19">
-        <v>4.271000056</v>
+        <v>4.251511824</v>
       </c>
       <c r="P19">
-        <v>10.456586344</v>
+        <v>10.408873776</v>
       </c>
       <c r="Q19">
-        <v>13.586586344</v>
+        <v>13.538873776</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1858993677205052</v>
+        <v>0.1871753280665603</v>
       </c>
       <c r="T19">
-        <v>0.8568302927478531</v>
+        <v>0.864633907386758</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.89164134600638</v>
+        <v>13.11988349345047</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1599121090145794</v>
+        <v>0.1596588828211396</v>
       </c>
       <c r="C20">
-        <v>127.1772571134921</v>
+        <v>126.1751632499126</v>
       </c>
       <c r="D20">
-        <v>150.1352571134921</v>
+        <v>150.4691632499126</v>
       </c>
       <c r="E20">
-        <v>-16.352</v>
+        <v>-15.016</v>
       </c>
       <c r="F20">
-        <v>24.048</v>
+        <v>25.384</v>
       </c>
       <c r="G20">
         <v>1.09</v>
@@ -3052,45 +3052,45 @@
         <v>15.87</v>
       </c>
       <c r="M20">
-        <v>1.2096144</v>
+        <v>1.3148912</v>
       </c>
       <c r="N20">
-        <v>14.6603856</v>
+        <v>14.5551088</v>
       </c>
       <c r="O20">
-        <v>4.251511824</v>
+        <v>4.220981552</v>
       </c>
       <c r="P20">
-        <v>10.408873776</v>
+        <v>10.334127248</v>
       </c>
       <c r="Q20">
-        <v>13.538873776</v>
+        <v>13.464127248</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1871753280665603</v>
+        <v>0.1884827936063452</v>
       </c>
       <c r="T20">
-        <v>0.864633907386758</v>
+        <v>0.872630203868599</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.29</v>
       </c>
       <c r="W20">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.11988349345048</v>
+        <v>12.06943966162371</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1596588828211396</v>
+        <v>0.1592139566276998</v>
       </c>
       <c r="C21">
-        <v>126.1751632499126</v>
+        <v>125.4294580780406</v>
       </c>
       <c r="D21">
-        <v>150.4691632499126</v>
+        <v>151.0594580780406</v>
       </c>
       <c r="E21">
-        <v>-15.016</v>
+        <v>-13.68</v>
       </c>
       <c r="F21">
-        <v>25.384</v>
+        <v>26.72</v>
       </c>
       <c r="G21">
         <v>1.09</v>
@@ -3134,28 +3134,28 @@
         <v>15.87</v>
       </c>
       <c r="M21">
-        <v>1.3148912</v>
+        <v>1.384096</v>
       </c>
       <c r="N21">
-        <v>14.5551088</v>
+        <v>14.485904</v>
       </c>
       <c r="O21">
-        <v>4.220981552</v>
+        <v>4.20091216</v>
       </c>
       <c r="P21">
-        <v>10.334127248</v>
+        <v>10.28499184</v>
       </c>
       <c r="Q21">
-        <v>13.464127248</v>
+        <v>13.41499184</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1884827936063452</v>
+        <v>0.1898229457846247</v>
       </c>
       <c r="T21">
-        <v>0.872630203868599</v>
+        <v>0.8808264077624861</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.06943966162371</v>
+        <v>11.46596767854253</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1592139566276998</v>
+        <v>0.1587690304342599</v>
       </c>
       <c r="C22">
-        <v>125.4294580780406</v>
+        <v>124.6884026341493</v>
       </c>
       <c r="D22">
-        <v>151.0594580780406</v>
+        <v>151.6544026341493</v>
       </c>
       <c r="E22">
-        <v>-13.68</v>
+        <v>-12.344</v>
       </c>
       <c r="F22">
-        <v>26.72</v>
+        <v>28.056</v>
       </c>
       <c r="G22">
         <v>1.09</v>
@@ -3216,28 +3216,28 @@
         <v>15.87</v>
       </c>
       <c r="M22">
-        <v>1.384096</v>
+        <v>1.4533008</v>
       </c>
       <c r="N22">
-        <v>14.485904</v>
+        <v>14.4166992</v>
       </c>
       <c r="O22">
-        <v>4.20091216</v>
+        <v>4.180842768</v>
       </c>
       <c r="P22">
-        <v>10.28499184</v>
+        <v>10.235856432</v>
       </c>
       <c r="Q22">
-        <v>13.41499184</v>
+        <v>13.365856432</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1898229457846247</v>
+        <v>0.1911970258661518</v>
       </c>
       <c r="T22">
-        <v>0.8808264077624861</v>
+        <v>0.8892301104891296</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.46596767854253</v>
+        <v>10.91996921765955</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1587690304342599</v>
+        <v>0.1583241042408201</v>
       </c>
       <c r="C23">
-        <v>124.6884026341493</v>
+        <v>123.9520520740417</v>
       </c>
       <c r="D23">
-        <v>151.6544026341493</v>
+        <v>152.2540520740417</v>
       </c>
       <c r="E23">
-        <v>-12.344</v>
+        <v>-11.008</v>
       </c>
       <c r="F23">
-        <v>28.056</v>
+        <v>29.392</v>
       </c>
       <c r="G23">
         <v>1.09</v>
@@ -3298,28 +3298,28 @@
         <v>15.87</v>
       </c>
       <c r="M23">
-        <v>1.4533008</v>
+        <v>1.5225056</v>
       </c>
       <c r="N23">
-        <v>14.4166992</v>
+        <v>14.3474944</v>
       </c>
       <c r="O23">
-        <v>4.180842768</v>
+        <v>4.160773375999999</v>
       </c>
       <c r="P23">
-        <v>10.235856432</v>
+        <v>10.186721024</v>
       </c>
       <c r="Q23">
-        <v>13.365856432</v>
+        <v>13.316721024</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1911970258661518</v>
+        <v>0.1926063387702822</v>
       </c>
       <c r="T23">
-        <v>0.8892301104891296</v>
+        <v>0.8978492927728666</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.91996921765955</v>
+        <v>10.42360698049321</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1583241042408201</v>
+        <v>0.1578791780473803</v>
       </c>
       <c r="C24">
-        <v>123.9520520740417</v>
+        <v>123.2204624293394</v>
       </c>
       <c r="D24">
-        <v>152.2540520740417</v>
+        <v>152.8584624293395</v>
       </c>
       <c r="E24">
-        <v>-11.008</v>
+        <v>-9.671999999999997</v>
       </c>
       <c r="F24">
-        <v>29.392</v>
+        <v>30.728</v>
       </c>
       <c r="G24">
         <v>1.09</v>
@@ -3380,28 +3380,28 @@
         <v>15.87</v>
       </c>
       <c r="M24">
-        <v>1.5225056</v>
+        <v>1.5917104</v>
       </c>
       <c r="N24">
-        <v>14.3474944</v>
+        <v>14.2782896</v>
       </c>
       <c r="O24">
-        <v>4.160773375999999</v>
+        <v>4.140703983999999</v>
       </c>
       <c r="P24">
-        <v>10.186721024</v>
+        <v>10.137585616</v>
       </c>
       <c r="Q24">
-        <v>13.316721024</v>
+        <v>13.267585616</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1926063387702822</v>
+        <v>0.19405225720439</v>
       </c>
       <c r="T24">
-        <v>0.8978492927728666</v>
+        <v>0.9066923499211165</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.42360698049321</v>
+        <v>9.970406676993504</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1578791780473803</v>
+        <v>0.1577239318539404</v>
       </c>
       <c r="C25">
-        <v>123.2204624293394</v>
+        <v>122.0964876328339</v>
       </c>
       <c r="D25">
-        <v>152.8584624293395</v>
+        <v>153.0704876328339</v>
       </c>
       <c r="E25">
-        <v>-9.671999999999997</v>
+        <v>-8.335999999999999</v>
       </c>
       <c r="F25">
-        <v>30.728</v>
+        <v>32.064</v>
       </c>
       <c r="G25">
         <v>1.09</v>
@@ -3462,45 +3462,45 @@
         <v>15.87</v>
       </c>
       <c r="M25">
-        <v>1.5917104</v>
+        <v>1.715424</v>
       </c>
       <c r="N25">
-        <v>14.2782896</v>
+        <v>14.154576</v>
       </c>
       <c r="O25">
-        <v>4.140703983999999</v>
+        <v>4.104827039999999</v>
       </c>
       <c r="P25">
-        <v>10.137585616</v>
+        <v>10.04974896</v>
       </c>
       <c r="Q25">
-        <v>13.267585616</v>
+        <v>13.17974896</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.19405225720439</v>
+        <v>0.1955362261236058</v>
       </c>
       <c r="T25">
-        <v>0.9066923499211165</v>
+        <v>0.9157681190995832</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.29</v>
       </c>
       <c r="W25">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.970406676993504</v>
+        <v>9.251357098886338</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1577239318539404</v>
+        <v>0.1572910756605006</v>
       </c>
       <c r="C26">
-        <v>122.0964876328339</v>
+        <v>121.3547729441218</v>
       </c>
       <c r="D26">
-        <v>153.0704876328339</v>
+        <v>153.6647729441218</v>
       </c>
       <c r="E26">
-        <v>-8.335999999999999</v>
+        <v>-7</v>
       </c>
       <c r="F26">
-        <v>32.064</v>
+        <v>33.4</v>
       </c>
       <c r="G26">
         <v>1.09</v>
@@ -3544,28 +3544,28 @@
         <v>15.87</v>
       </c>
       <c r="M26">
-        <v>1.715424</v>
+        <v>1.7869</v>
       </c>
       <c r="N26">
-        <v>14.154576</v>
+        <v>14.0831</v>
       </c>
       <c r="O26">
-        <v>4.104827039999999</v>
+        <v>4.084099</v>
       </c>
       <c r="P26">
-        <v>10.04974896</v>
+        <v>9.999001</v>
       </c>
       <c r="Q26">
-        <v>13.17974896</v>
+        <v>13.129001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1955362261236058</v>
+        <v>0.1970597675473341</v>
       </c>
       <c r="T26">
-        <v>0.9157681190995832</v>
+        <v>0.9250859087894757</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.251357098886338</v>
+        <v>8.881302814930887</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1572910756605006</v>
+        <v>0.1568582194670607</v>
       </c>
       <c r="C27">
-        <v>121.3547729441218</v>
+        <v>120.6176907820052</v>
       </c>
       <c r="D27">
-        <v>153.6647729441218</v>
+        <v>154.2636907820052</v>
       </c>
       <c r="E27">
-        <v>-7</v>
+        <v>-5.664000000000001</v>
       </c>
       <c r="F27">
-        <v>33.4</v>
+        <v>34.736</v>
       </c>
       <c r="G27">
         <v>1.09</v>
@@ -3626,28 +3626,28 @@
         <v>15.87</v>
       </c>
       <c r="M27">
-        <v>1.7869</v>
+        <v>1.858376</v>
       </c>
       <c r="N27">
-        <v>14.0831</v>
+        <v>14.011624</v>
       </c>
       <c r="O27">
-        <v>4.084099</v>
+        <v>4.063370959999999</v>
       </c>
       <c r="P27">
-        <v>9.999001</v>
+        <v>9.948253040000001</v>
       </c>
       <c r="Q27">
-        <v>13.129001</v>
+        <v>13.07825304</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1970597675473341</v>
+        <v>0.1986244857662983</v>
       </c>
       <c r="T27">
-        <v>0.9250859087894757</v>
+        <v>0.9346555306331493</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.881302814930887</v>
+        <v>8.539714245125852</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1568582194670607</v>
+        <v>0.1564253632736209</v>
       </c>
       <c r="C28">
-        <v>120.6176907820052</v>
+        <v>119.885295525094</v>
       </c>
       <c r="D28">
-        <v>154.2636907820052</v>
+        <v>154.867295525094</v>
       </c>
       <c r="E28">
-        <v>-5.664000000000001</v>
+        <v>-4.327999999999996</v>
       </c>
       <c r="F28">
-        <v>34.736</v>
+        <v>36.072</v>
       </c>
       <c r="G28">
         <v>1.09</v>
@@ -3708,28 +3708,28 @@
         <v>15.87</v>
       </c>
       <c r="M28">
-        <v>1.858376</v>
+        <v>1.929852</v>
       </c>
       <c r="N28">
-        <v>14.011624</v>
+        <v>13.940148</v>
       </c>
       <c r="O28">
-        <v>4.063370959999999</v>
+        <v>4.04264292</v>
       </c>
       <c r="P28">
-        <v>9.948253040000001</v>
+        <v>9.897505079999998</v>
       </c>
       <c r="Q28">
-        <v>13.07825304</v>
+        <v>13.02750508</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1986244857662983</v>
+        <v>0.2002320729775628</v>
       </c>
       <c r="T28">
-        <v>0.9346555306331493</v>
+        <v>0.9444873338971973</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.539714245125852</v>
+        <v>8.223428532343412</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1564253632736209</v>
+        <v>0.1559925070801811</v>
       </c>
       <c r="C29">
-        <v>119.885295525094</v>
+        <v>119.1576424064344</v>
       </c>
       <c r="D29">
-        <v>154.867295525094</v>
+        <v>155.4756424064344</v>
       </c>
       <c r="E29">
-        <v>-4.327999999999996</v>
+        <v>-2.991999999999997</v>
       </c>
       <c r="F29">
-        <v>36.072</v>
+        <v>37.408</v>
       </c>
       <c r="G29">
         <v>1.09</v>
@@ -3790,28 +3790,28 @@
         <v>15.87</v>
       </c>
       <c r="M29">
-        <v>1.929852</v>
+        <v>2.001328</v>
       </c>
       <c r="N29">
-        <v>13.940148</v>
+        <v>13.868672</v>
       </c>
       <c r="O29">
-        <v>4.04264292</v>
+        <v>4.02191488</v>
       </c>
       <c r="P29">
-        <v>9.897505079999998</v>
+        <v>9.846757119999999</v>
       </c>
       <c r="Q29">
-        <v>13.02750508</v>
+        <v>12.97675712</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2002320729775628</v>
+        <v>0.2018843153891404</v>
       </c>
       <c r="T29">
-        <v>0.9444873338971973</v>
+        <v>0.954592242807469</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.223428532343412</v>
+        <v>7.929734656188291</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1559925070801811</v>
+        <v>0.1555596508867412</v>
       </c>
       <c r="C30">
-        <v>119.1576424064344</v>
+        <v>118.4347875303571</v>
       </c>
       <c r="D30">
-        <v>155.4756424064344</v>
+        <v>156.0887875303571</v>
       </c>
       <c r="E30">
-        <v>-2.991999999999997</v>
+        <v>-1.655999999999999</v>
       </c>
       <c r="F30">
-        <v>37.408</v>
+        <v>38.744</v>
       </c>
       <c r="G30">
         <v>1.09</v>
@@ -3872,28 +3872,28 @@
         <v>15.87</v>
       </c>
       <c r="M30">
-        <v>2.001328</v>
+        <v>2.072804</v>
       </c>
       <c r="N30">
-        <v>13.868672</v>
+        <v>13.797196</v>
       </c>
       <c r="O30">
-        <v>4.02191488</v>
+        <v>4.00118684</v>
       </c>
       <c r="P30">
-        <v>9.846757119999999</v>
+        <v>9.796009160000001</v>
       </c>
       <c r="Q30">
-        <v>12.97675712</v>
+        <v>12.92600916</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2018843153891404</v>
+        <v>0.2035830998404806</v>
       </c>
       <c r="T30">
-        <v>0.954592242807469</v>
+        <v>0.9649817970391568</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.929734656188291</v>
+        <v>7.656295530112832</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1555596508867412</v>
+        <v>0.1552971946933014</v>
       </c>
       <c r="C31">
-        <v>118.4347875303571</v>
+        <v>117.4729201200422</v>
       </c>
       <c r="D31">
-        <v>156.0887875303571</v>
+        <v>156.4629201200422</v>
       </c>
       <c r="E31">
-        <v>-1.656000000000006</v>
+        <v>-0.3200000000000003</v>
       </c>
       <c r="F31">
-        <v>38.74399999999999</v>
+        <v>40.08</v>
       </c>
       <c r="G31">
         <v>1.09</v>
@@ -3954,45 +3954,45 @@
         <v>15.87</v>
       </c>
       <c r="M31">
-        <v>2.072804</v>
+        <v>2.176344</v>
       </c>
       <c r="N31">
-        <v>13.797196</v>
+        <v>13.693656</v>
       </c>
       <c r="O31">
-        <v>4.00118684</v>
+        <v>3.971160239999999</v>
       </c>
       <c r="P31">
-        <v>9.796009160000001</v>
+        <v>9.722495759999999</v>
       </c>
       <c r="Q31">
-        <v>12.92600916</v>
+        <v>12.85249576</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2035830998404806</v>
+        <v>0.2053304209904305</v>
       </c>
       <c r="T31">
-        <v>0.9649817970391568</v>
+        <v>0.9756681956774641</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.29</v>
       </c>
       <c r="W31">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.656295530112834</v>
+        <v>7.292045742768607</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1552971946933014</v>
+        <v>0.1548700184998615</v>
       </c>
       <c r="C32">
-        <v>117.4729201200422</v>
+        <v>116.7497121187109</v>
       </c>
       <c r="D32">
-        <v>156.4629201200422</v>
+        <v>157.0757121187109</v>
       </c>
       <c r="E32">
-        <v>-0.3200000000000003</v>
+        <v>1.015999999999998</v>
       </c>
       <c r="F32">
-        <v>40.08</v>
+        <v>41.416</v>
       </c>
       <c r="G32">
         <v>1.09</v>
@@ -4036,28 +4036,28 @@
         <v>15.87</v>
       </c>
       <c r="M32">
-        <v>2.176344</v>
+        <v>2.2488888</v>
       </c>
       <c r="N32">
-        <v>13.693656</v>
+        <v>13.6211112</v>
       </c>
       <c r="O32">
-        <v>3.971160239999999</v>
+        <v>3.950122248</v>
       </c>
       <c r="P32">
-        <v>9.722495759999999</v>
+        <v>9.670988952</v>
       </c>
       <c r="Q32">
-        <v>12.85249576</v>
+        <v>12.800988952</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2053304209904305</v>
+        <v>0.2071283891302341</v>
       </c>
       <c r="T32">
-        <v>0.9756681956774641</v>
+        <v>0.9866643450009398</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.292045742768607</v>
+        <v>7.056818460743813</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1548700184998615</v>
+        <v>0.1544428423064217</v>
       </c>
       <c r="C33">
-        <v>116.7497121187109</v>
+        <v>116.0313230294736</v>
       </c>
       <c r="D33">
-        <v>157.0757121187109</v>
+        <v>157.6933230294736</v>
       </c>
       <c r="E33">
-        <v>1.015999999999998</v>
+        <v>2.352000000000004</v>
       </c>
       <c r="F33">
-        <v>41.416</v>
+        <v>42.752</v>
       </c>
       <c r="G33">
         <v>1.09</v>
@@ -4118,28 +4118,28 @@
         <v>15.87</v>
       </c>
       <c r="M33">
-        <v>2.2488888</v>
+        <v>2.3214336</v>
       </c>
       <c r="N33">
-        <v>13.6211112</v>
+        <v>13.5485664</v>
       </c>
       <c r="O33">
-        <v>3.950122248</v>
+        <v>3.929084255999999</v>
       </c>
       <c r="P33">
-        <v>9.670988952</v>
+        <v>9.619482143999999</v>
       </c>
       <c r="Q33">
-        <v>12.800988952</v>
+        <v>12.749482144</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2071283891302341</v>
+        <v>0.2089792386859143</v>
       </c>
       <c r="T33">
-        <v>0.9866643450009398</v>
+        <v>0.9979839104809884</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.056818460743813</v>
+        <v>6.836292883845568</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1544428423064217</v>
+        <v>0.1540156661129818</v>
       </c>
       <c r="C34">
-        <v>116.0313230294736</v>
+        <v>115.3178099196092</v>
       </c>
       <c r="D34">
-        <v>157.6933230294736</v>
+        <v>158.3158099196092</v>
       </c>
       <c r="E34">
-        <v>2.352000000000004</v>
+        <v>3.688000000000002</v>
       </c>
       <c r="F34">
-        <v>42.752</v>
+        <v>44.088</v>
       </c>
       <c r="G34">
         <v>1.09</v>
@@ -4200,28 +4200,28 @@
         <v>15.87</v>
       </c>
       <c r="M34">
-        <v>2.3214336</v>
+        <v>2.3939784</v>
       </c>
       <c r="N34">
-        <v>13.5485664</v>
+        <v>13.4760216</v>
       </c>
       <c r="O34">
-        <v>3.929084255999999</v>
+        <v>3.908046263999999</v>
       </c>
       <c r="P34">
-        <v>9.619482143999999</v>
+        <v>9.567975336</v>
       </c>
       <c r="Q34">
-        <v>12.749482144</v>
+        <v>12.697975336</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2089792386859143</v>
+        <v>0.2108853374820625</v>
       </c>
       <c r="T34">
-        <v>0.9979839104809884</v>
+        <v>1.009641373438053</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.836292883845568</v>
+        <v>6.629132493426006</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1540156661129818</v>
+        <v>0.153588489919542</v>
       </c>
       <c r="C35">
-        <v>115.3178099196092</v>
+        <v>114.6092307610486</v>
       </c>
       <c r="D35">
-        <v>158.3158099196092</v>
+        <v>158.9432307610486</v>
       </c>
       <c r="E35">
-        <v>3.688000000000002</v>
+        <v>5.024000000000001</v>
       </c>
       <c r="F35">
-        <v>44.088</v>
+        <v>45.424</v>
       </c>
       <c r="G35">
         <v>1.09</v>
@@ -4282,28 +4282,28 @@
         <v>15.87</v>
       </c>
       <c r="M35">
-        <v>2.3939784</v>
+        <v>2.4665232</v>
       </c>
       <c r="N35">
-        <v>13.4760216</v>
+        <v>13.4034768</v>
       </c>
       <c r="O35">
-        <v>3.908046263999999</v>
+        <v>3.887008272</v>
       </c>
       <c r="P35">
-        <v>9.567975336</v>
+        <v>9.516468528000001</v>
       </c>
       <c r="Q35">
-        <v>12.697975336</v>
+        <v>12.646468528</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2108853374820625</v>
+        <v>0.2128491968477909</v>
       </c>
       <c r="T35">
-        <v>1.009641373438053</v>
+        <v>1.021652092848363</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.629132493426006</v>
+        <v>6.434158008325241</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.153588489919542</v>
+        <v>0.1531613137261021</v>
       </c>
       <c r="C36">
-        <v>114.6092307610486</v>
+        <v>113.9056444483732</v>
       </c>
       <c r="D36">
-        <v>158.9432307610486</v>
+        <v>159.5756444483732</v>
       </c>
       <c r="E36">
-        <v>5.024000000000001</v>
+        <v>6.360000000000007</v>
       </c>
       <c r="F36">
-        <v>45.424</v>
+        <v>46.76000000000001</v>
       </c>
       <c r="G36">
         <v>1.09</v>
@@ -4364,28 +4364,28 @@
         <v>15.87</v>
       </c>
       <c r="M36">
-        <v>2.4665232</v>
+        <v>2.539068</v>
       </c>
       <c r="N36">
-        <v>13.4034768</v>
+        <v>13.330932</v>
       </c>
       <c r="O36">
-        <v>3.887008272</v>
+        <v>3.86597028</v>
       </c>
       <c r="P36">
-        <v>9.516468528000001</v>
+        <v>9.46496172</v>
       </c>
       <c r="Q36">
-        <v>12.646468528</v>
+        <v>12.59496172</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2128491968477909</v>
+        <v>0.2148734826555418</v>
       </c>
       <c r="T36">
-        <v>1.021652092848363</v>
+        <v>1.034032372855912</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.434158008325241</v>
+        <v>6.25032492237309</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1531613137261021</v>
+        <v>0.1529897375326623</v>
       </c>
       <c r="C37">
-        <v>113.9056444483732</v>
+        <v>112.8250735805867</v>
       </c>
       <c r="D37">
-        <v>159.5756444483732</v>
+        <v>159.8310735805867</v>
       </c>
       <c r="E37">
-        <v>6.360000000000007</v>
+        <v>7.696000000000005</v>
       </c>
       <c r="F37">
-        <v>46.76000000000001</v>
+        <v>48.096</v>
       </c>
       <c r="G37">
         <v>1.09</v>
@@ -4446,45 +4446,45 @@
         <v>15.87</v>
       </c>
       <c r="M37">
-        <v>2.539068</v>
+        <v>2.6597088</v>
       </c>
       <c r="N37">
-        <v>13.330932</v>
+        <v>13.2102912</v>
       </c>
       <c r="O37">
-        <v>3.86597028</v>
+        <v>3.830984447999999</v>
       </c>
       <c r="P37">
-        <v>9.46496172</v>
+        <v>9.379306752</v>
       </c>
       <c r="Q37">
-        <v>12.59496172</v>
+        <v>12.509306752</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2148734826555418</v>
+        <v>0.2169610273947849</v>
       </c>
       <c r="T37">
-        <v>1.034032372855912</v>
+        <v>1.046799536613698</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.29</v>
       </c>
       <c r="W37">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.25032492237309</v>
+        <v>5.966818623151526</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1529897375326623</v>
+        <v>0.1525696613392225</v>
       </c>
       <c r="C38">
-        <v>112.8250735805866</v>
+        <v>112.117915408321</v>
       </c>
       <c r="D38">
-        <v>159.8310735805866</v>
+        <v>160.459915408321</v>
       </c>
       <c r="E38">
-        <v>7.695999999999998</v>
+        <v>9.031999999999996</v>
       </c>
       <c r="F38">
-        <v>48.096</v>
+        <v>49.432</v>
       </c>
       <c r="G38">
         <v>1.09</v>
@@ -4528,28 +4528,28 @@
         <v>15.87</v>
       </c>
       <c r="M38">
-        <v>2.6597088</v>
+        <v>2.7335896</v>
       </c>
       <c r="N38">
-        <v>13.2102912</v>
+        <v>13.1364104</v>
       </c>
       <c r="O38">
-        <v>3.830984448</v>
+        <v>3.809559015999999</v>
       </c>
       <c r="P38">
-        <v>9.379306752000002</v>
+        <v>9.326851383999999</v>
       </c>
       <c r="Q38">
-        <v>12.509306752</v>
+        <v>12.456851384</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2169610273947849</v>
+        <v>0.2191148433955913</v>
       </c>
       <c r="T38">
-        <v>1.046799536613698</v>
+        <v>1.059972007157445</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.966818623151528</v>
+        <v>5.805553254958243</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1525696613392225</v>
+        <v>0.1521495851457826</v>
       </c>
       <c r="C39">
-        <v>112.117915408321</v>
+        <v>111.4157250312924</v>
       </c>
       <c r="D39">
-        <v>160.459915408321</v>
+        <v>161.0937250312924</v>
       </c>
       <c r="E39">
-        <v>9.031999999999996</v>
+        <v>10.368</v>
       </c>
       <c r="F39">
-        <v>49.432</v>
+        <v>50.768</v>
       </c>
       <c r="G39">
         <v>1.09</v>
@@ -4610,28 +4610,28 @@
         <v>15.87</v>
       </c>
       <c r="M39">
-        <v>2.7335896</v>
+        <v>2.8074704</v>
       </c>
       <c r="N39">
-        <v>13.1364104</v>
+        <v>13.0625296</v>
       </c>
       <c r="O39">
-        <v>3.809559015999999</v>
+        <v>3.788133584</v>
       </c>
       <c r="P39">
-        <v>9.326851383999999</v>
+        <v>9.274396016000001</v>
       </c>
       <c r="Q39">
-        <v>12.456851384</v>
+        <v>12.404396016</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2191148433955913</v>
+        <v>0.2213381373319075</v>
       </c>
       <c r="T39">
-        <v>1.059972007157445</v>
+        <v>1.073569396105828</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.805553254958243</v>
+        <v>5.652775537722499</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1521495851457826</v>
+        <v>0.1517295089523428</v>
       </c>
       <c r="C40">
-        <v>111.4157250312924</v>
+        <v>110.718561550667</v>
       </c>
       <c r="D40">
-        <v>161.0937250312924</v>
+        <v>161.732561550667</v>
       </c>
       <c r="E40">
-        <v>10.368</v>
+        <v>11.704</v>
       </c>
       <c r="F40">
-        <v>50.768</v>
+        <v>52.104</v>
       </c>
       <c r="G40">
         <v>1.09</v>
@@ -4692,28 +4692,28 @@
         <v>15.87</v>
       </c>
       <c r="M40">
-        <v>2.8074704</v>
+        <v>2.8813512</v>
       </c>
       <c r="N40">
-        <v>13.0625296</v>
+        <v>12.9886488</v>
       </c>
       <c r="O40">
-        <v>3.788133584</v>
+        <v>3.766708152</v>
       </c>
       <c r="P40">
-        <v>9.274396016000001</v>
+        <v>9.221940648</v>
       </c>
       <c r="Q40">
-        <v>12.404396016</v>
+        <v>12.351940648</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2213381373319075</v>
+        <v>0.2236343261513817</v>
       </c>
       <c r="T40">
-        <v>1.073569396105828</v>
+        <v>1.087612601085307</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.652775537722499</v>
+        <v>5.507832575216794</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1517295089523428</v>
+        <v>0.151309432758903</v>
       </c>
       <c r="C41">
-        <v>110.718561550667</v>
+        <v>110.0264850088353</v>
       </c>
       <c r="D41">
-        <v>161.732561550667</v>
+        <v>162.3764850088353</v>
       </c>
       <c r="E41">
-        <v>11.704</v>
+        <v>13.04</v>
       </c>
       <c r="F41">
-        <v>52.104</v>
+        <v>53.44</v>
       </c>
       <c r="G41">
         <v>1.09</v>
@@ -4774,28 +4774,28 @@
         <v>15.87</v>
       </c>
       <c r="M41">
-        <v>2.8813512</v>
+        <v>2.955232</v>
       </c>
       <c r="N41">
-        <v>12.9886488</v>
+        <v>12.914768</v>
       </c>
       <c r="O41">
-        <v>3.766708152</v>
+        <v>3.745282719999999</v>
       </c>
       <c r="P41">
-        <v>9.221940648</v>
+        <v>9.16948528</v>
       </c>
       <c r="Q41">
-        <v>12.351940648</v>
+        <v>12.29948528</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2236343261513817</v>
+        <v>0.2260070545981716</v>
       </c>
       <c r="T41">
-        <v>1.087612601085307</v>
+        <v>1.102123912897435</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.507832575216794</v>
+        <v>5.370136760836374</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.151309432758903</v>
+        <v>0.1508893565654631</v>
       </c>
       <c r="C42">
-        <v>110.0264850088353</v>
+        <v>109.3395564082226</v>
       </c>
       <c r="D42">
-        <v>162.3764850088353</v>
+        <v>163.0255564082226</v>
       </c>
       <c r="E42">
-        <v>13.04</v>
+        <v>14.376</v>
       </c>
       <c r="F42">
-        <v>53.44</v>
+        <v>54.776</v>
       </c>
       <c r="G42">
         <v>1.09</v>
@@ -4856,28 +4856,28 @@
         <v>15.87</v>
       </c>
       <c r="M42">
-        <v>2.955232</v>
+        <v>3.0291128</v>
       </c>
       <c r="N42">
-        <v>12.914768</v>
+        <v>12.8408872</v>
       </c>
       <c r="O42">
-        <v>3.745282719999999</v>
+        <v>3.723857288</v>
       </c>
       <c r="P42">
-        <v>9.16948528</v>
+        <v>9.117029912</v>
       </c>
       <c r="Q42">
-        <v>12.29948528</v>
+        <v>12.247029912</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2260070545981716</v>
+        <v>0.2284602145177341</v>
       </c>
       <c r="T42">
-        <v>1.102123912897435</v>
+        <v>1.11712713358455</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.370136760836374</v>
+        <v>5.23915781545012</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1508893565654631</v>
+        <v>0.1504692803720233</v>
       </c>
       <c r="C43">
-        <v>109.3395564082226</v>
+        <v>108.6578377305549</v>
       </c>
       <c r="D43">
-        <v>163.0255564082226</v>
+        <v>163.6798377305549</v>
       </c>
       <c r="E43">
-        <v>14.376</v>
+        <v>15.712</v>
       </c>
       <c r="F43">
-        <v>54.776</v>
+        <v>56.112</v>
       </c>
       <c r="G43">
         <v>1.09</v>
@@ -4938,28 +4938,28 @@
         <v>15.87</v>
       </c>
       <c r="M43">
-        <v>3.0291128</v>
+        <v>3.1029936</v>
       </c>
       <c r="N43">
-        <v>12.8408872</v>
+        <v>12.7670064</v>
       </c>
       <c r="O43">
-        <v>3.723857288</v>
+        <v>3.702431856</v>
       </c>
       <c r="P43">
-        <v>9.117029912</v>
+        <v>9.064574543999999</v>
       </c>
       <c r="Q43">
-        <v>12.247029912</v>
+        <v>12.194574544</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2284602145177341</v>
+        <v>0.2309979661586608</v>
       </c>
       <c r="T43">
-        <v>1.11712713358455</v>
+        <v>1.132647706709152</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.23915781545012</v>
+        <v>5.114415962701309</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1504692803720233</v>
+        <v>0.1500492041785834</v>
       </c>
       <c r="C44">
-        <v>108.6578377305549</v>
+        <v>107.9813919565892</v>
       </c>
       <c r="D44">
-        <v>163.6798377305549</v>
+        <v>164.3393919565892</v>
       </c>
       <c r="E44">
-        <v>15.712</v>
+        <v>17.04799999999999</v>
       </c>
       <c r="F44">
-        <v>56.11199999999999</v>
+        <v>57.44799999999999</v>
       </c>
       <c r="G44">
         <v>1.09</v>
@@ -5020,28 +5020,28 @@
         <v>15.87</v>
       </c>
       <c r="M44">
-        <v>3.1029936</v>
+        <v>3.1768744</v>
       </c>
       <c r="N44">
-        <v>12.7670064</v>
+        <v>12.6931256</v>
       </c>
       <c r="O44">
-        <v>3.702431856</v>
+        <v>3.681006424</v>
       </c>
       <c r="P44">
-        <v>9.064574543999999</v>
+        <v>9.012119176000001</v>
       </c>
       <c r="Q44">
-        <v>12.194574544</v>
+        <v>12.142119176</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2309979661586608</v>
+        <v>0.233624761716813</v>
       </c>
       <c r="T44">
-        <v>1.132647706709152</v>
+        <v>1.148712861346898</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.114415962701309</v>
+        <v>4.995476056591976</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1500492041785834</v>
+        <v>0.1496291279851436</v>
       </c>
       <c r="C45">
-        <v>107.9813919565892</v>
+        <v>107.3102830863232</v>
       </c>
       <c r="D45">
-        <v>164.3393919565892</v>
+        <v>165.0042830863232</v>
       </c>
       <c r="E45">
-        <v>17.04799999999999</v>
+        <v>18.384</v>
       </c>
       <c r="F45">
-        <v>57.44799999999999</v>
+        <v>58.784</v>
       </c>
       <c r="G45">
         <v>1.09</v>
@@ -5102,28 +5102,28 @@
         <v>15.87</v>
       </c>
       <c r="M45">
-        <v>3.1768744</v>
+        <v>3.2507552</v>
       </c>
       <c r="N45">
-        <v>12.6931256</v>
+        <v>12.6192448</v>
       </c>
       <c r="O45">
-        <v>3.681006424</v>
+        <v>3.659580992</v>
       </c>
       <c r="P45">
-        <v>9.012119176000001</v>
+        <v>8.959663807999998</v>
       </c>
       <c r="Q45">
-        <v>12.142119176</v>
+        <v>12.089663808</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.233624761716813</v>
+        <v>0.2363453714020422</v>
       </c>
       <c r="T45">
-        <v>1.148712861346898</v>
+        <v>1.16535177150742</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.995476056591976</v>
+        <v>4.88194250985125</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1496291279851436</v>
+        <v>0.1492090517917038</v>
       </c>
       <c r="C46">
-        <v>107.3102830863232</v>
+        <v>106.6445761596974</v>
       </c>
       <c r="D46">
-        <v>165.0042830863232</v>
+        <v>165.6745761596974</v>
       </c>
       <c r="E46">
-        <v>18.384</v>
+        <v>19.72</v>
       </c>
       <c r="F46">
-        <v>58.784</v>
+        <v>60.12</v>
       </c>
       <c r="G46">
         <v>1.09</v>
@@ -5184,28 +5184,28 @@
         <v>15.87</v>
       </c>
       <c r="M46">
-        <v>3.2507552</v>
+        <v>3.324636</v>
       </c>
       <c r="N46">
-        <v>12.6192448</v>
+        <v>12.545364</v>
       </c>
       <c r="O46">
-        <v>3.659580992</v>
+        <v>3.63815556</v>
       </c>
       <c r="P46">
-        <v>8.959663807999998</v>
+        <v>8.90720844</v>
       </c>
       <c r="Q46">
-        <v>12.089663808</v>
+        <v>12.03720844</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2363453714020422</v>
+        <v>0.2391649123485523</v>
       </c>
       <c r="T46">
-        <v>1.16535177150742</v>
+        <v>1.182595732946507</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.88194250985125</v>
+        <v>4.773454898521221</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1492090517917038</v>
+        <v>0.148788975598264</v>
       </c>
       <c r="C47">
-        <v>106.6445761596974</v>
+        <v>105.9843372778039</v>
       </c>
       <c r="D47">
-        <v>165.6745761596974</v>
+        <v>166.3503372778039</v>
       </c>
       <c r="E47">
-        <v>19.72</v>
+        <v>21.056</v>
       </c>
       <c r="F47">
-        <v>60.12</v>
+        <v>61.456</v>
       </c>
       <c r="G47">
         <v>1.09</v>
@@ -5266,28 +5266,28 @@
         <v>15.87</v>
       </c>
       <c r="M47">
-        <v>3.324636</v>
+        <v>3.3985168</v>
       </c>
       <c r="N47">
-        <v>12.545364</v>
+        <v>12.4714832</v>
       </c>
       <c r="O47">
-        <v>3.63815556</v>
+        <v>3.616730127999999</v>
       </c>
       <c r="P47">
-        <v>8.90720844</v>
+        <v>8.854753071999999</v>
       </c>
       <c r="Q47">
-        <v>12.03720844</v>
+        <v>11.984753072</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2391649123485523</v>
+        <v>0.2420888807375258</v>
       </c>
       <c r="T47">
-        <v>1.182595732946507</v>
+        <v>1.200478359624079</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.773454898521221</v>
+        <v>4.669684139857716</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.148788975598264</v>
+        <v>0.1483688994048241</v>
       </c>
       <c r="C48">
-        <v>105.9843372778039</v>
+        <v>105.3296336246165</v>
       </c>
       <c r="D48">
-        <v>166.3503372778039</v>
+        <v>167.0316336246165</v>
       </c>
       <c r="E48">
-        <v>21.056</v>
+        <v>22.392</v>
       </c>
       <c r="F48">
-        <v>61.456</v>
+        <v>62.792</v>
       </c>
       <c r="G48">
         <v>1.09</v>
@@ -5348,28 +5348,28 @@
         <v>15.87</v>
       </c>
       <c r="M48">
-        <v>3.3985168</v>
+        <v>3.4723976</v>
       </c>
       <c r="N48">
-        <v>12.4714832</v>
+        <v>12.3976024</v>
       </c>
       <c r="O48">
-        <v>3.616730127999999</v>
+        <v>3.595304695999999</v>
       </c>
       <c r="P48">
-        <v>8.854753071999999</v>
+        <v>8.802297703999999</v>
       </c>
       <c r="Q48">
-        <v>11.984753072</v>
+        <v>11.932297704</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2420888807375258</v>
+        <v>0.2451231875562719</v>
       </c>
       <c r="T48">
-        <v>1.200478359624079</v>
+        <v>1.219035802402691</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.669684139857716</v>
+        <v>4.570329158158616</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1483688994048241</v>
+        <v>0.1488008232113842</v>
       </c>
       <c r="C49">
-        <v>105.3296336246165</v>
+        <v>103.2932029216206</v>
       </c>
       <c r="D49">
-        <v>167.0316336246165</v>
+        <v>166.3312029216206</v>
       </c>
       <c r="E49">
-        <v>22.392</v>
+        <v>23.728</v>
       </c>
       <c r="F49">
-        <v>62.792</v>
+        <v>64.128</v>
       </c>
       <c r="G49">
         <v>1.09</v>
@@ -5430,45 +5430,45 @@
         <v>15.87</v>
       </c>
       <c r="M49">
-        <v>3.4723976</v>
+        <v>3.7065984</v>
       </c>
       <c r="N49">
-        <v>12.3976024</v>
+        <v>12.1634016</v>
       </c>
       <c r="O49">
-        <v>3.595304695999999</v>
+        <v>3.527386463999999</v>
       </c>
       <c r="P49">
-        <v>8.802297703999999</v>
+        <v>8.636015135999999</v>
       </c>
       <c r="Q49">
-        <v>11.932297704</v>
+        <v>11.766015136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2451231875562719</v>
+        <v>0.2482741984834312</v>
       </c>
       <c r="T49">
-        <v>1.219035802402691</v>
+        <v>1.23830699298048</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.29</v>
       </c>
       <c r="W49">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.570329158158616</v>
+        <v>4.281553674657605</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1488008232113842</v>
+        <v>0.1483984970179444</v>
       </c>
       <c r="C50">
-        <v>103.2932029216206</v>
+        <v>102.609448341064</v>
       </c>
       <c r="D50">
-        <v>166.3312029216206</v>
+        <v>166.983448341064</v>
       </c>
       <c r="E50">
-        <v>23.728</v>
+        <v>25.064</v>
       </c>
       <c r="F50">
-        <v>64.128</v>
+        <v>65.464</v>
       </c>
       <c r="G50">
         <v>1.09</v>
@@ -5512,28 +5512,28 @@
         <v>15.87</v>
       </c>
       <c r="M50">
-        <v>3.7065984</v>
+        <v>3.7838192</v>
       </c>
       <c r="N50">
-        <v>12.1634016</v>
+        <v>12.0861808</v>
       </c>
       <c r="O50">
-        <v>3.527386463999999</v>
+        <v>3.504992431999999</v>
       </c>
       <c r="P50">
-        <v>8.636015135999999</v>
+        <v>8.581188367999999</v>
       </c>
       <c r="Q50">
-        <v>11.766015136</v>
+        <v>11.711188368</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2482741984834312</v>
+        <v>0.2515487784665577</v>
       </c>
       <c r="T50">
-        <v>1.23830699298048</v>
+        <v>1.258333916522104</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.281553674657605</v>
+        <v>4.194175028236021</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1483984970179444</v>
+        <v>0.1479961708245046</v>
       </c>
       <c r="C51">
-        <v>102.609448341064</v>
+        <v>101.9308292839751</v>
       </c>
       <c r="D51">
-        <v>166.983448341064</v>
+        <v>167.6408292839751</v>
       </c>
       <c r="E51">
-        <v>25.064</v>
+        <v>26.4</v>
       </c>
       <c r="F51">
-        <v>65.464</v>
+        <v>66.8</v>
       </c>
       <c r="G51">
         <v>1.09</v>
@@ -5594,28 +5594,28 @@
         <v>15.87</v>
       </c>
       <c r="M51">
-        <v>3.7838192</v>
+        <v>3.86104</v>
       </c>
       <c r="N51">
-        <v>12.0861808</v>
+        <v>12.00896</v>
       </c>
       <c r="O51">
-        <v>3.504992431999999</v>
+        <v>3.482598399999999</v>
       </c>
       <c r="P51">
-        <v>8.581188367999999</v>
+        <v>8.5263616</v>
       </c>
       <c r="Q51">
-        <v>11.711188368</v>
+        <v>11.6563616</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2515487784665577</v>
+        <v>0.2549543416490092</v>
       </c>
       <c r="T51">
-        <v>1.258333916522104</v>
+        <v>1.279161917005394</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.194175028236021</v>
+        <v>4.110291527671301</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1479961708245046</v>
+        <v>0.1475938446310647</v>
       </c>
       <c r="C52">
-        <v>101.9308292839751</v>
+        <v>101.257406642708</v>
       </c>
       <c r="D52">
-        <v>167.6408292839751</v>
+        <v>168.303406642708</v>
       </c>
       <c r="E52">
-        <v>26.4</v>
+        <v>27.736</v>
       </c>
       <c r="F52">
-        <v>66.8</v>
+        <v>68.136</v>
       </c>
       <c r="G52">
         <v>1.09</v>
@@ -5676,28 +5676,28 @@
         <v>15.87</v>
       </c>
       <c r="M52">
-        <v>3.86104</v>
+        <v>3.9382608</v>
       </c>
       <c r="N52">
-        <v>12.00896</v>
+        <v>11.9317392</v>
       </c>
       <c r="O52">
-        <v>3.482598399999999</v>
+        <v>3.460204367999999</v>
       </c>
       <c r="P52">
-        <v>8.5263616</v>
+        <v>8.471534832</v>
       </c>
       <c r="Q52">
-        <v>11.6563616</v>
+        <v>11.601534832</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2549543416490092</v>
+        <v>0.2584989074103362</v>
       </c>
       <c r="T52">
-        <v>1.279161917005394</v>
+        <v>1.300840039957389</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.110291527671301</v>
+        <v>4.029697576148334</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1475938446310647</v>
+        <v>0.1484837184376249</v>
       </c>
       <c r="C53">
-        <v>101.257406642708</v>
+        <v>98.46286194443472</v>
       </c>
       <c r="D53">
-        <v>168.303406642708</v>
+        <v>166.8448619444347</v>
       </c>
       <c r="E53">
-        <v>27.736</v>
+        <v>29.072</v>
       </c>
       <c r="F53">
-        <v>68.136</v>
+        <v>69.47199999999999</v>
       </c>
       <c r="G53">
         <v>1.09</v>
@@ -5758,45 +5758,45 @@
         <v>15.87</v>
       </c>
       <c r="M53">
-        <v>3.9382608</v>
+        <v>4.2586336</v>
       </c>
       <c r="N53">
-        <v>11.9317392</v>
+        <v>11.6113664</v>
       </c>
       <c r="O53">
-        <v>3.460204367999999</v>
+        <v>3.367296255999999</v>
       </c>
       <c r="P53">
-        <v>8.471534832</v>
+        <v>8.244070144</v>
       </c>
       <c r="Q53">
-        <v>11.601534832</v>
+        <v>11.374070144</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2584989074103362</v>
+        <v>0.2621911634117185</v>
       </c>
       <c r="T53">
-        <v>1.300840039957389</v>
+        <v>1.323421418032384</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.29</v>
       </c>
       <c r="W53">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.029697576148334</v>
+        <v>3.726547407130776</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1484837184376249</v>
+        <v>0.1481062422441851</v>
       </c>
       <c r="C54">
-        <v>98.46286194443472</v>
+        <v>97.7424642967472</v>
       </c>
       <c r="D54">
-        <v>166.8448619444347</v>
+        <v>167.4604642967472</v>
       </c>
       <c r="E54">
-        <v>29.072</v>
+        <v>30.40800000000001</v>
       </c>
       <c r="F54">
-        <v>69.47199999999999</v>
+        <v>70.80800000000001</v>
       </c>
       <c r="G54">
         <v>1.09</v>
@@ -5840,28 +5840,28 @@
         <v>15.87</v>
       </c>
       <c r="M54">
-        <v>4.2586336</v>
+        <v>4.3405304</v>
       </c>
       <c r="N54">
-        <v>11.6113664</v>
+        <v>11.5294696</v>
       </c>
       <c r="O54">
-        <v>3.367296255999999</v>
+        <v>3.343546184</v>
       </c>
       <c r="P54">
-        <v>8.244070144</v>
+        <v>8.185923416</v>
       </c>
       <c r="Q54">
-        <v>11.374070144</v>
+        <v>11.315923416</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2621911634117185</v>
+        <v>0.2660405366897554</v>
       </c>
       <c r="T54">
-        <v>1.323421418032384</v>
+        <v>1.346963705812697</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.726547407130776</v>
+        <v>3.656235191901892</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1481062422441851</v>
+        <v>0.1477287660507452</v>
       </c>
       <c r="C55">
-        <v>97.7424642967472</v>
+        <v>97.02662621044038</v>
       </c>
       <c r="D55">
-        <v>167.4604642967472</v>
+        <v>168.0806262104404</v>
       </c>
       <c r="E55">
-        <v>30.40800000000001</v>
+        <v>31.74400000000001</v>
       </c>
       <c r="F55">
-        <v>70.80800000000001</v>
+        <v>72.14400000000001</v>
       </c>
       <c r="G55">
         <v>1.09</v>
@@ -5922,28 +5922,28 @@
         <v>15.87</v>
       </c>
       <c r="M55">
-        <v>4.3405304</v>
+        <v>4.4224272</v>
       </c>
       <c r="N55">
-        <v>11.5294696</v>
+        <v>11.4475728</v>
       </c>
       <c r="O55">
-        <v>3.343546184</v>
+        <v>3.319796112</v>
       </c>
       <c r="P55">
-        <v>8.185923416</v>
+        <v>8.127776688000001</v>
       </c>
       <c r="Q55">
-        <v>11.315923416</v>
+        <v>11.257776688</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2660405366897554</v>
+        <v>0.2700572740233591</v>
       </c>
       <c r="T55">
-        <v>1.346963705812697</v>
+        <v>1.37152957132259</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.656235191901892</v>
+        <v>3.588527132792598</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1477287660507452</v>
+        <v>0.1473512898573054</v>
       </c>
       <c r="C56">
-        <v>97.02662621044038</v>
+        <v>96.31539853053646</v>
       </c>
       <c r="D56">
-        <v>168.0806262104404</v>
+        <v>168.7053985305365</v>
       </c>
       <c r="E56">
-        <v>31.74400000000001</v>
+        <v>33.08000000000001</v>
       </c>
       <c r="F56">
-        <v>72.14400000000001</v>
+        <v>73.48</v>
       </c>
       <c r="G56">
         <v>1.09</v>
@@ -6004,28 +6004,28 @@
         <v>15.87</v>
       </c>
       <c r="M56">
-        <v>4.4224272</v>
+        <v>4.504324</v>
       </c>
       <c r="N56">
-        <v>11.4475728</v>
+        <v>11.365676</v>
       </c>
       <c r="O56">
-        <v>3.319796112</v>
+        <v>3.296046039999999</v>
       </c>
       <c r="P56">
-        <v>8.127776688000001</v>
+        <v>8.06962996</v>
       </c>
       <c r="Q56">
-        <v>11.257776688</v>
+        <v>11.19962996</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2700572740233591</v>
+        <v>0.2742525330162341</v>
       </c>
       <c r="T56">
-        <v>1.37152957132259</v>
+        <v>1.397187253077367</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.588527132792598</v>
+        <v>3.523281184923642</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1473512898573054</v>
+        <v>0.1480870936638655</v>
       </c>
       <c r="C57">
-        <v>96.31539853053646</v>
+        <v>93.76581361009727</v>
       </c>
       <c r="D57">
-        <v>168.7053985305365</v>
+        <v>167.4918136100973</v>
       </c>
       <c r="E57">
-        <v>33.08000000000001</v>
+        <v>34.416</v>
       </c>
       <c r="F57">
-        <v>73.48</v>
+        <v>74.816</v>
       </c>
       <c r="G57">
         <v>1.09</v>
@@ -6086,45 +6086,45 @@
         <v>15.87</v>
       </c>
       <c r="M57">
-        <v>4.504324</v>
+        <v>4.795705600000001</v>
       </c>
       <c r="N57">
-        <v>11.365676</v>
+        <v>11.0742944</v>
       </c>
       <c r="O57">
-        <v>3.296046039999999</v>
+        <v>3.211545376</v>
       </c>
       <c r="P57">
-        <v>8.06962996</v>
+        <v>7.862749023999999</v>
       </c>
       <c r="Q57">
-        <v>11.19962996</v>
+        <v>10.992749024</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2742525330162341</v>
+        <v>0.2786384855996944</v>
       </c>
       <c r="T57">
-        <v>1.397187253077367</v>
+        <v>1.424011193093724</v>
       </c>
       <c r="U57">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V57">
         <v>0.29</v>
       </c>
       <c r="W57">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>3.523281184923642</v>
+        <v>3.309210640452991</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1480870936638655</v>
+        <v>0.1477294974704257</v>
       </c>
       <c r="C58">
-        <v>93.76581361009727</v>
+        <v>93.01742010738901</v>
       </c>
       <c r="D58">
-        <v>167.4918136100973</v>
+        <v>168.079420107389</v>
       </c>
       <c r="E58">
-        <v>34.416</v>
+        <v>35.752</v>
       </c>
       <c r="F58">
-        <v>74.816</v>
+        <v>76.152</v>
       </c>
       <c r="G58">
         <v>1.09</v>
@@ -6168,28 +6168,28 @@
         <v>15.87</v>
       </c>
       <c r="M58">
-        <v>4.795705600000001</v>
+        <v>4.881343200000001</v>
       </c>
       <c r="N58">
-        <v>11.0742944</v>
+        <v>10.9886568</v>
       </c>
       <c r="O58">
-        <v>3.211545376</v>
+        <v>3.186710471999999</v>
       </c>
       <c r="P58">
-        <v>7.862749023999999</v>
+        <v>7.801946327999998</v>
       </c>
       <c r="Q58">
-        <v>10.992749024</v>
+        <v>10.931946328</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2786384855996944</v>
+        <v>0.2832284359777342</v>
       </c>
       <c r="T58">
-        <v>1.424011193093724</v>
+        <v>1.452082758227121</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.309210640452991</v>
+        <v>3.2511543134275</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1477294974704257</v>
+        <v>0.1473719012769859</v>
       </c>
       <c r="C59">
-        <v>93.01742010738901</v>
+        <v>92.27316408451586</v>
       </c>
       <c r="D59">
-        <v>168.079420107389</v>
+        <v>168.6711640845159</v>
       </c>
       <c r="E59">
-        <v>35.752</v>
+        <v>37.088</v>
       </c>
       <c r="F59">
-        <v>76.152</v>
+        <v>77.488</v>
       </c>
       <c r="G59">
         <v>1.09</v>
@@ -6250,28 +6250,28 @@
         <v>15.87</v>
       </c>
       <c r="M59">
-        <v>4.881343200000001</v>
+        <v>4.9669808</v>
       </c>
       <c r="N59">
-        <v>10.9886568</v>
+        <v>10.9030192</v>
       </c>
       <c r="O59">
-        <v>3.186710471999999</v>
+        <v>3.161875568</v>
       </c>
       <c r="P59">
-        <v>7.801946327999998</v>
+        <v>7.741143632</v>
       </c>
       <c r="Q59">
-        <v>10.931946328</v>
+        <v>10.871143632</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2832284359777342</v>
+        <v>0.2880369554213949</v>
       </c>
       <c r="T59">
-        <v>1.452082758227121</v>
+        <v>1.481491064557347</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.2511543134275</v>
+        <v>3.195099928713233</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1473719012769859</v>
+        <v>0.147014305083546</v>
       </c>
       <c r="C60">
-        <v>92.27316408451587</v>
+        <v>91.53308939536889</v>
       </c>
       <c r="D60">
-        <v>168.6711640845159</v>
+        <v>169.2670893953689</v>
       </c>
       <c r="E60">
-        <v>37.08799999999999</v>
+        <v>38.424</v>
       </c>
       <c r="F60">
-        <v>77.48799999999999</v>
+        <v>78.824</v>
       </c>
       <c r="G60">
         <v>1.09</v>
@@ -6332,28 +6332,28 @@
         <v>15.87</v>
       </c>
       <c r="M60">
-        <v>4.966980799999999</v>
+        <v>5.0526184</v>
       </c>
       <c r="N60">
-        <v>10.9030192</v>
+        <v>10.8173816</v>
       </c>
       <c r="O60">
-        <v>3.161875568</v>
+        <v>3.137040664</v>
       </c>
       <c r="P60">
-        <v>7.741143632</v>
+        <v>7.680340935999999</v>
       </c>
       <c r="Q60">
-        <v>10.871143632</v>
+        <v>10.810340936</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2880369554213948</v>
+        <v>0.2930800367891366</v>
       </c>
       <c r="T60">
-        <v>1.481491064557347</v>
+        <v>1.512333922415876</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.195099928713234</v>
+        <v>3.140945692633348</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.147014305083546</v>
+        <v>0.1466567088901062</v>
       </c>
       <c r="C61">
-        <v>91.53308939536889</v>
+        <v>90.79724051579043</v>
       </c>
       <c r="D61">
-        <v>169.2670893953689</v>
+        <v>169.8672405157904</v>
       </c>
       <c r="E61">
-        <v>38.424</v>
+        <v>39.76</v>
       </c>
       <c r="F61">
-        <v>78.824</v>
+        <v>80.16</v>
       </c>
       <c r="G61">
         <v>1.09</v>
@@ -6414,28 +6414,28 @@
         <v>15.87</v>
       </c>
       <c r="M61">
-        <v>5.0526184</v>
+        <v>5.138256</v>
       </c>
       <c r="N61">
-        <v>10.8173816</v>
+        <v>10.731744</v>
       </c>
       <c r="O61">
-        <v>3.137040664</v>
+        <v>3.11220576</v>
       </c>
       <c r="P61">
-        <v>7.680340935999999</v>
+        <v>7.619538239999999</v>
       </c>
       <c r="Q61">
-        <v>10.810340936</v>
+        <v>10.74953824</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2930800367891366</v>
+        <v>0.2983752722252654</v>
       </c>
       <c r="T61">
-        <v>1.512333922415876</v>
+        <v>1.544718923167332</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.140945692633348</v>
+        <v>3.088596597756125</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1466567088901062</v>
+        <v>0.1462991126966663</v>
       </c>
       <c r="C62">
-        <v>90.79724051579043</v>
+        <v>90.06566255463885</v>
       </c>
       <c r="D62">
-        <v>169.8672405157904</v>
+        <v>170.4716625546388</v>
       </c>
       <c r="E62">
-        <v>39.76</v>
+        <v>41.096</v>
       </c>
       <c r="F62">
-        <v>80.16</v>
+        <v>81.496</v>
       </c>
       <c r="G62">
         <v>1.09</v>
@@ -6496,28 +6496,28 @@
         <v>15.87</v>
       </c>
       <c r="M62">
-        <v>5.138256</v>
+        <v>5.2238936</v>
       </c>
       <c r="N62">
-        <v>10.731744</v>
+        <v>10.6461064</v>
       </c>
       <c r="O62">
-        <v>3.11220576</v>
+        <v>3.087370855999999</v>
       </c>
       <c r="P62">
-        <v>7.619538239999999</v>
+        <v>7.558735543999999</v>
       </c>
       <c r="Q62">
-        <v>10.74953824</v>
+        <v>10.688735544</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2983752722252654</v>
+        <v>0.3039420581965803</v>
       </c>
       <c r="T62">
-        <v>1.544718923167332</v>
+        <v>1.578764693188093</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.088596597756125</v>
+        <v>3.037963866645369</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1462991126966663</v>
+        <v>0.1493750765032265</v>
       </c>
       <c r="C63">
-        <v>90.06566255463885</v>
+        <v>83.66700962919433</v>
       </c>
       <c r="D63">
-        <v>170.4716625546388</v>
+        <v>165.4090096291943</v>
       </c>
       <c r="E63">
-        <v>41.096</v>
+        <v>42.432</v>
       </c>
       <c r="F63">
-        <v>81.496</v>
+        <v>82.83199999999999</v>
       </c>
       <c r="G63">
         <v>1.09</v>
@@ -6578,45 +6578,45 @@
         <v>15.87</v>
       </c>
       <c r="M63">
-        <v>5.2238936</v>
+        <v>5.9556208</v>
       </c>
       <c r="N63">
-        <v>10.6461064</v>
+        <v>9.914379199999999</v>
       </c>
       <c r="O63">
-        <v>3.087370855999999</v>
+        <v>2.875169967999999</v>
       </c>
       <c r="P63">
-        <v>7.558735543999999</v>
+        <v>7.039209231999999</v>
       </c>
       <c r="Q63">
-        <v>10.688735544</v>
+        <v>10.169209232</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3039420581965803</v>
+        <v>0.3098018329032275</v>
       </c>
       <c r="T63">
-        <v>1.578764693188093</v>
+        <v>1.614602345841526</v>
       </c>
       <c r="U63">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V63">
         <v>0.29</v>
       </c>
       <c r="W63">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.037963866645369</v>
+        <v>2.664709613479757</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1493750765032265</v>
+        <v>0.1490728603097866</v>
       </c>
       <c r="C64">
-        <v>83.66700962919433</v>
+        <v>82.8150601445072</v>
       </c>
       <c r="D64">
-        <v>165.4090096291943</v>
+        <v>165.8930601445072</v>
       </c>
       <c r="E64">
-        <v>42.432</v>
+        <v>43.76799999999999</v>
       </c>
       <c r="F64">
-        <v>82.83199999999999</v>
+        <v>84.16799999999999</v>
       </c>
       <c r="G64">
         <v>1.09</v>
@@ -6660,28 +6660,28 @@
         <v>15.87</v>
       </c>
       <c r="M64">
-        <v>5.9556208</v>
+        <v>6.0516792</v>
       </c>
       <c r="N64">
-        <v>9.914379199999999</v>
+        <v>9.818320799999999</v>
       </c>
       <c r="O64">
-        <v>2.875169967999999</v>
+        <v>2.847313031999999</v>
       </c>
       <c r="P64">
-        <v>7.039209231999999</v>
+        <v>6.971007768</v>
       </c>
       <c r="Q64">
-        <v>10.169209232</v>
+        <v>10.101007768</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3098018329032275</v>
+        <v>0.3159783521886125</v>
       </c>
       <c r="T64">
-        <v>1.614602345841526</v>
+        <v>1.652377168908659</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.664709613479757</v>
+        <v>2.622412635488014</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1490728603097866</v>
+        <v>0.1487706441163468</v>
       </c>
       <c r="C65">
-        <v>82.8150601445072</v>
+        <v>81.96595201145824</v>
       </c>
       <c r="D65">
-        <v>165.8930601445072</v>
+        <v>166.3799520114582</v>
       </c>
       <c r="E65">
-        <v>43.76799999999999</v>
+        <v>45.10400000000001</v>
       </c>
       <c r="F65">
-        <v>84.16799999999999</v>
+        <v>85.504</v>
       </c>
       <c r="G65">
         <v>1.09</v>
@@ -6742,28 +6742,28 @@
         <v>15.87</v>
       </c>
       <c r="M65">
-        <v>6.0516792</v>
+        <v>6.147737600000001</v>
       </c>
       <c r="N65">
-        <v>9.818320799999999</v>
+        <v>9.722262399999998</v>
       </c>
       <c r="O65">
-        <v>2.847313031999999</v>
+        <v>2.819456095999999</v>
       </c>
       <c r="P65">
-        <v>6.971007768</v>
+        <v>6.902806303999999</v>
       </c>
       <c r="Q65">
-        <v>10.101007768</v>
+        <v>10.032806304</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3159783521886125</v>
+        <v>0.3224980114342967</v>
       </c>
       <c r="T65">
-        <v>1.652377168908659</v>
+        <v>1.692250593257298</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.622412635488014</v>
+        <v>2.581437438058514</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1487706441163468</v>
+        <v>0.148468427922907</v>
       </c>
       <c r="C66">
-        <v>81.96595201145824</v>
+        <v>81.11971032157246</v>
       </c>
       <c r="D66">
-        <v>166.3799520114582</v>
+        <v>166.8697103215725</v>
       </c>
       <c r="E66">
-        <v>45.10400000000001</v>
+        <v>46.44</v>
       </c>
       <c r="F66">
-        <v>85.504</v>
+        <v>86.84</v>
       </c>
       <c r="G66">
         <v>1.09</v>
@@ -6824,28 +6824,28 @@
         <v>15.87</v>
       </c>
       <c r="M66">
-        <v>6.147737600000001</v>
+        <v>6.243796000000001</v>
       </c>
       <c r="N66">
-        <v>9.722262399999998</v>
+        <v>9.626203999999998</v>
       </c>
       <c r="O66">
-        <v>2.819456095999999</v>
+        <v>2.791599159999999</v>
       </c>
       <c r="P66">
-        <v>6.902806303999999</v>
+        <v>6.834604839999999</v>
       </c>
       <c r="Q66">
-        <v>10.032806304</v>
+        <v>9.96460484</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3224980114342967</v>
+        <v>0.329390222636877</v>
       </c>
       <c r="T66">
-        <v>1.692250593257298</v>
+        <v>1.734402498997288</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.581437438058514</v>
+        <v>2.541723015934537</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.148468427922907</v>
+        <v>0.1481662117294671</v>
       </c>
       <c r="C67">
-        <v>81.11971032157246</v>
+        <v>80.27636046268613</v>
       </c>
       <c r="D67">
-        <v>166.8697103215725</v>
+        <v>167.3623604626861</v>
       </c>
       <c r="E67">
-        <v>46.44</v>
+        <v>47.776</v>
       </c>
       <c r="F67">
-        <v>86.84</v>
+        <v>88.176</v>
       </c>
       <c r="G67">
         <v>1.09</v>
@@ -6906,28 +6906,28 @@
         <v>15.87</v>
       </c>
       <c r="M67">
-        <v>6.243796000000001</v>
+        <v>6.339854400000001</v>
       </c>
       <c r="N67">
-        <v>9.626203999999998</v>
+        <v>9.530145599999997</v>
       </c>
       <c r="O67">
-        <v>2.791599159999999</v>
+        <v>2.763742223999999</v>
       </c>
       <c r="P67">
-        <v>6.834604839999999</v>
+        <v>6.766403375999998</v>
       </c>
       <c r="Q67">
-        <v>9.96460484</v>
+        <v>9.896403375999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.329390222636877</v>
+        <v>0.3366878580278445</v>
       </c>
       <c r="T67">
-        <v>1.734402498997288</v>
+        <v>1.779033928604337</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.541723015934537</v>
+        <v>2.50321206114765</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1481662117294671</v>
+        <v>0.1497192255360273</v>
       </c>
       <c r="C68">
-        <v>80.27636046268613</v>
+        <v>76.43922503604708</v>
       </c>
       <c r="D68">
-        <v>167.3623604626861</v>
+        <v>164.8612250360471</v>
       </c>
       <c r="E68">
-        <v>47.776</v>
+        <v>49.112</v>
       </c>
       <c r="F68">
-        <v>88.176</v>
+        <v>89.512</v>
       </c>
       <c r="G68">
         <v>1.09</v>
@@ -6988,45 +6988,45 @@
         <v>15.87</v>
       </c>
       <c r="M68">
-        <v>6.339854400000001</v>
+        <v>6.7850096</v>
       </c>
       <c r="N68">
-        <v>9.530145599999997</v>
+        <v>9.084990399999999</v>
       </c>
       <c r="O68">
-        <v>2.763742223999999</v>
+        <v>2.634647215999999</v>
       </c>
       <c r="P68">
-        <v>6.766403375999998</v>
+        <v>6.450343183999999</v>
       </c>
       <c r="Q68">
-        <v>9.896403375999999</v>
+        <v>9.580343184</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3366878580278445</v>
+        <v>0.3444277743515978</v>
       </c>
       <c r="T68">
-        <v>1.779033928604337</v>
+        <v>1.826370293339085</v>
       </c>
       <c r="U68">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V68">
         <v>0.29</v>
       </c>
       <c r="W68">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>2.50321206114765</v>
+        <v>2.338979741458287</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1497192255360273</v>
+        <v>0.1494446993425874</v>
       </c>
       <c r="C69">
-        <v>76.43922503604708</v>
+        <v>75.53989690486476</v>
       </c>
       <c r="D69">
-        <v>164.8612250360471</v>
+        <v>165.2978969048648</v>
       </c>
       <c r="E69">
-        <v>49.112</v>
+        <v>50.448</v>
       </c>
       <c r="F69">
-        <v>89.512</v>
+        <v>90.848</v>
       </c>
       <c r="G69">
         <v>1.09</v>
@@ -7070,28 +7070,28 @@
         <v>15.87</v>
       </c>
       <c r="M69">
-        <v>6.7850096</v>
+        <v>6.8862784</v>
       </c>
       <c r="N69">
-        <v>9.084990399999999</v>
+        <v>8.983721599999999</v>
       </c>
       <c r="O69">
-        <v>2.634647215999999</v>
+        <v>2.605279264</v>
       </c>
       <c r="P69">
-        <v>6.450343183999999</v>
+        <v>6.378442335999999</v>
       </c>
       <c r="Q69">
-        <v>9.580343184</v>
+        <v>9.508442336</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3444277743515978</v>
+        <v>0.3526514354455858</v>
       </c>
       <c r="T69">
-        <v>1.826370293339085</v>
+        <v>1.876665180869755</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.338979741458287</v>
+        <v>2.304582980554489</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1494446993425874</v>
+        <v>0.1491701731491476</v>
       </c>
       <c r="C70">
-        <v>75.53989690486476</v>
+        <v>74.64288816354659</v>
       </c>
       <c r="D70">
-        <v>165.2978969048648</v>
+        <v>165.7368881635466</v>
       </c>
       <c r="E70">
-        <v>50.448</v>
+        <v>51.784</v>
       </c>
       <c r="F70">
-        <v>90.848</v>
+        <v>92.184</v>
       </c>
       <c r="G70">
         <v>1.09</v>
@@ -7152,28 +7152,28 @@
         <v>15.87</v>
       </c>
       <c r="M70">
-        <v>6.8862784</v>
+        <v>6.987547200000001</v>
       </c>
       <c r="N70">
-        <v>8.983721599999999</v>
+        <v>8.882452799999999</v>
       </c>
       <c r="O70">
-        <v>2.605279264</v>
+        <v>2.575911312</v>
       </c>
       <c r="P70">
-        <v>6.378442335999999</v>
+        <v>6.306541488</v>
       </c>
       <c r="Q70">
-        <v>9.508442336</v>
+        <v>9.436541488</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3526514354455858</v>
+        <v>0.361405655319831</v>
       </c>
       <c r="T70">
-        <v>1.876665180869755</v>
+        <v>1.930204899854018</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.304582980554489</v>
+        <v>2.27118322721312</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1491701731491476</v>
+        <v>0.1488956469557078</v>
       </c>
       <c r="C71">
-        <v>74.64288816354659</v>
+        <v>73.74821734051613</v>
       </c>
       <c r="D71">
-        <v>165.7368881635466</v>
+        <v>166.1782173405161</v>
       </c>
       <c r="E71">
-        <v>51.784</v>
+        <v>53.12000000000001</v>
       </c>
       <c r="F71">
-        <v>92.184</v>
+        <v>93.52000000000001</v>
       </c>
       <c r="G71">
         <v>1.09</v>
@@ -7234,28 +7234,28 @@
         <v>15.87</v>
       </c>
       <c r="M71">
-        <v>6.987547200000001</v>
+        <v>7.088816000000001</v>
       </c>
       <c r="N71">
-        <v>8.882452799999999</v>
+        <v>8.781183999999998</v>
       </c>
       <c r="O71">
-        <v>2.575911312</v>
+        <v>2.546543359999999</v>
       </c>
       <c r="P71">
-        <v>6.306541488</v>
+        <v>6.234640639999999</v>
       </c>
       <c r="Q71">
-        <v>9.436541488</v>
+        <v>9.364640639999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.361405655319831</v>
+        <v>0.3707434898523593</v>
       </c>
       <c r="T71">
-        <v>1.930204899854018</v>
+        <v>1.98731393343723</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.27118322721312</v>
+        <v>2.238737752538646</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1488956469557078</v>
+        <v>0.1486211207622679</v>
       </c>
       <c r="C72">
-        <v>73.74821734051613</v>
+        <v>72.85590316207599</v>
       </c>
       <c r="D72">
-        <v>166.1782173405161</v>
+        <v>166.621903162076</v>
       </c>
       <c r="E72">
-        <v>53.12000000000001</v>
+        <v>54.45600000000001</v>
       </c>
       <c r="F72">
-        <v>93.52000000000001</v>
+        <v>94.85600000000001</v>
       </c>
       <c r="G72">
         <v>1.09</v>
@@ -7316,28 +7316,28 @@
         <v>15.87</v>
       </c>
       <c r="M72">
-        <v>7.088816000000001</v>
+        <v>7.190084800000001</v>
       </c>
       <c r="N72">
-        <v>8.781183999999998</v>
+        <v>8.679915199999998</v>
       </c>
       <c r="O72">
-        <v>2.546543359999999</v>
+        <v>2.517175408</v>
       </c>
       <c r="P72">
-        <v>6.234640639999999</v>
+        <v>6.162739791999998</v>
       </c>
       <c r="Q72">
-        <v>9.364640639999999</v>
+        <v>9.292739791999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3707434898523593</v>
+        <v>0.3807253129733377</v>
       </c>
       <c r="T72">
-        <v>1.98731393343723</v>
+        <v>2.048361521060664</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.238737752538646</v>
+        <v>2.207206234897257</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1486211207622679</v>
+        <v>0.1483465945688281</v>
       </c>
       <c r="C73">
-        <v>72.85590316207598</v>
+        <v>71.96596455505654</v>
       </c>
       <c r="D73">
-        <v>166.621903162076</v>
+        <v>167.0679645550565</v>
       </c>
       <c r="E73">
-        <v>54.456</v>
+        <v>55.79199999999999</v>
       </c>
       <c r="F73">
-        <v>94.85599999999999</v>
+        <v>96.19199999999999</v>
       </c>
       <c r="G73">
         <v>1.09</v>
@@ -7398,28 +7398,28 @@
         <v>15.87</v>
       </c>
       <c r="M73">
-        <v>7.1900848</v>
+        <v>7.2913536</v>
       </c>
       <c r="N73">
-        <v>8.6799152</v>
+        <v>8.5786464</v>
       </c>
       <c r="O73">
-        <v>2.517175408</v>
+        <v>2.487807456</v>
       </c>
       <c r="P73">
-        <v>6.162739792</v>
+        <v>6.090838944</v>
       </c>
       <c r="Q73">
-        <v>9.292739792000001</v>
+        <v>9.220838944</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3807253129733377</v>
+        <v>0.3914201234601002</v>
       </c>
       <c r="T73">
-        <v>2.048361521060664</v>
+        <v>2.1137696506572</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.207206234897257</v>
+        <v>2.176550592745906</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1483465945688281</v>
+        <v>0.1480720683753882</v>
       </c>
       <c r="C74">
-        <v>71.96596455505654</v>
+        <v>71.07842064950751</v>
       </c>
       <c r="D74">
-        <v>167.0679645550565</v>
+        <v>167.5164206495075</v>
       </c>
       <c r="E74">
-        <v>55.79199999999999</v>
+        <v>57.12799999999999</v>
       </c>
       <c r="F74">
-        <v>96.19199999999999</v>
+        <v>97.52799999999999</v>
       </c>
       <c r="G74">
         <v>1.09</v>
@@ -7480,28 +7480,28 @@
         <v>15.87</v>
       </c>
       <c r="M74">
-        <v>7.2913536</v>
+        <v>7.3926224</v>
       </c>
       <c r="N74">
-        <v>8.5786464</v>
+        <v>8.477377600000001</v>
       </c>
       <c r="O74">
-        <v>2.487807456</v>
+        <v>2.458439504</v>
       </c>
       <c r="P74">
-        <v>6.090838944</v>
+        <v>6.018938096000001</v>
       </c>
       <c r="Q74">
-        <v>9.220838944</v>
+        <v>9.148938096000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3914201234601002</v>
+        <v>0.4029071421310675</v>
       </c>
       <c r="T74">
-        <v>2.1137696506572</v>
+        <v>2.184022826890517</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.176550592745906</v>
+        <v>2.146734831201442</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1480720683753882</v>
+        <v>0.1477975421819484</v>
       </c>
       <c r="C75">
-        <v>71.07842064950751</v>
+        <v>70.19329078143222</v>
       </c>
       <c r="D75">
-        <v>167.5164206495075</v>
+        <v>167.9672907814322</v>
       </c>
       <c r="E75">
-        <v>57.12799999999999</v>
+        <v>58.46399999999999</v>
       </c>
       <c r="F75">
-        <v>97.52799999999999</v>
+        <v>98.86399999999999</v>
       </c>
       <c r="G75">
         <v>1.09</v>
@@ -7562,28 +7562,28 @@
         <v>15.87</v>
       </c>
       <c r="M75">
-        <v>7.3926224</v>
+        <v>7.4938912</v>
       </c>
       <c r="N75">
-        <v>8.477377600000001</v>
+        <v>8.376108799999999</v>
       </c>
       <c r="O75">
-        <v>2.458439504</v>
+        <v>2.429071551999999</v>
       </c>
       <c r="P75">
-        <v>6.018938096000001</v>
+        <v>5.947037247999999</v>
       </c>
       <c r="Q75">
-        <v>9.148938096000002</v>
+        <v>9.077037248</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4029071421310675</v>
+        <v>0.4152777776228784</v>
       </c>
       <c r="T75">
-        <v>2.184022826890517</v>
+        <v>2.25968009360332</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.146734831201442</v>
+        <v>2.117724901050071</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1477975421819484</v>
+        <v>0.1475230159885086</v>
       </c>
       <c r="C76">
-        <v>70.19329078143222</v>
+        <v>69.31059449556747</v>
       </c>
       <c r="D76">
-        <v>167.9672907814322</v>
+        <v>168.4205944955675</v>
       </c>
       <c r="E76">
-        <v>58.46399999999999</v>
+        <v>59.79999999999999</v>
       </c>
       <c r="F76">
-        <v>98.86399999999999</v>
+        <v>100.2</v>
       </c>
       <c r="G76">
         <v>1.09</v>
@@ -7644,28 +7644,28 @@
         <v>15.87</v>
       </c>
       <c r="M76">
-        <v>7.4938912</v>
+        <v>7.59516</v>
       </c>
       <c r="N76">
-        <v>8.376108799999999</v>
+        <v>8.274839999999999</v>
       </c>
       <c r="O76">
-        <v>2.429071551999999</v>
+        <v>2.3997036</v>
       </c>
       <c r="P76">
-        <v>5.947037247999999</v>
+        <v>5.8751364</v>
       </c>
       <c r="Q76">
-        <v>9.077037248</v>
+        <v>9.005136400000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4152777776228784</v>
+        <v>0.4286380639540342</v>
       </c>
       <c r="T76">
-        <v>2.25968009360332</v>
+        <v>2.341389941653147</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.117724901050071</v>
+        <v>2.08948856903607</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1475230159885086</v>
+        <v>0.1472484897950687</v>
       </c>
       <c r="C77">
-        <v>69.31059449556747</v>
+        <v>68.43035154820706</v>
       </c>
       <c r="D77">
-        <v>168.4205944955675</v>
+        <v>168.8763515482071</v>
       </c>
       <c r="E77">
-        <v>59.79999999999999</v>
+        <v>61.136</v>
       </c>
       <c r="F77">
-        <v>100.2</v>
+        <v>101.536</v>
       </c>
       <c r="G77">
         <v>1.09</v>
@@ -7726,28 +7726,28 @@
         <v>15.87</v>
       </c>
       <c r="M77">
-        <v>7.59516</v>
+        <v>7.696428800000001</v>
       </c>
       <c r="N77">
-        <v>8.274839999999999</v>
+        <v>8.173571199999998</v>
       </c>
       <c r="O77">
-        <v>2.3997036</v>
+        <v>2.370335647999999</v>
       </c>
       <c r="P77">
-        <v>5.8751364</v>
+        <v>5.803235551999999</v>
       </c>
       <c r="Q77">
-        <v>9.005136400000001</v>
+        <v>8.933235551999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4286380639540342</v>
+        <v>0.4431117074794531</v>
       </c>
       <c r="T77">
-        <v>2.341389941653147</v>
+        <v>2.429908943707127</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.08948856903607</v>
+        <v>2.061995298390858</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1472484897950687</v>
+        <v>0.1469739636016289</v>
       </c>
       <c r="C78">
-        <v>68.43035154820706</v>
+        <v>67.55258191007256</v>
       </c>
       <c r="D78">
-        <v>168.8763515482071</v>
+        <v>169.3345819100726</v>
       </c>
       <c r="E78">
-        <v>61.136</v>
+        <v>62.472</v>
       </c>
       <c r="F78">
-        <v>101.536</v>
+        <v>102.872</v>
       </c>
       <c r="G78">
         <v>1.09</v>
@@ -7808,28 +7808,28 @@
         <v>15.87</v>
       </c>
       <c r="M78">
-        <v>7.696428800000001</v>
+        <v>7.7976976</v>
       </c>
       <c r="N78">
-        <v>8.173571199999998</v>
+        <v>8.072302399999998</v>
       </c>
       <c r="O78">
-        <v>2.370335647999999</v>
+        <v>2.340967695999999</v>
       </c>
       <c r="P78">
-        <v>5.803235551999999</v>
+        <v>5.731334703999998</v>
       </c>
       <c r="Q78">
-        <v>8.933235551999999</v>
+        <v>8.861334703999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4431117074794531</v>
+        <v>0.4588439287027343</v>
       </c>
       <c r="T78">
-        <v>2.429908943707127</v>
+        <v>2.52612525028754</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.061995298390858</v>
+        <v>2.035216138671497</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1469739636016289</v>
+        <v>0.1466994374081891</v>
       </c>
       <c r="C79">
-        <v>67.55258191007256</v>
+        <v>66.6773057692298</v>
       </c>
       <c r="D79">
-        <v>169.3345819100726</v>
+        <v>169.7953057692298</v>
       </c>
       <c r="E79">
-        <v>62.472</v>
+        <v>63.808</v>
       </c>
       <c r="F79">
-        <v>102.872</v>
+        <v>104.208</v>
       </c>
       <c r="G79">
         <v>1.09</v>
@@ -7890,28 +7890,28 @@
         <v>15.87</v>
       </c>
       <c r="M79">
-        <v>7.7976976</v>
+        <v>7.898966400000001</v>
       </c>
       <c r="N79">
-        <v>8.072302399999998</v>
+        <v>7.971033599999998</v>
       </c>
       <c r="O79">
-        <v>2.340967695999999</v>
+        <v>2.311599744</v>
       </c>
       <c r="P79">
-        <v>5.731334703999998</v>
+        <v>5.659433855999999</v>
       </c>
       <c r="Q79">
-        <v>8.861334703999999</v>
+        <v>8.789433855999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4588439287027343</v>
+        <v>0.4760063518554048</v>
       </c>
       <c r="T79">
-        <v>2.52612525028754</v>
+        <v>2.631088493829808</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.035216138671497</v>
+        <v>2.009123624073144</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1466994374081891</v>
+        <v>0.1543896912147492</v>
       </c>
       <c r="C80">
-        <v>66.6773057692298</v>
+        <v>53.31650873812352</v>
       </c>
       <c r="D80">
-        <v>169.7953057692298</v>
+        <v>157.7705087381235</v>
       </c>
       <c r="E80">
-        <v>63.808</v>
+        <v>65.14400000000001</v>
       </c>
       <c r="F80">
-        <v>104.208</v>
+        <v>105.544</v>
       </c>
       <c r="G80">
         <v>1.09</v>
@@ -7972,45 +7972,45 @@
         <v>15.87</v>
       </c>
       <c r="M80">
-        <v>7.898966400000001</v>
+        <v>9.498959999999999</v>
       </c>
       <c r="N80">
-        <v>7.971033599999998</v>
+        <v>6.371040000000001</v>
       </c>
       <c r="O80">
-        <v>2.311599744</v>
+        <v>1.8476016</v>
       </c>
       <c r="P80">
-        <v>5.659433855999999</v>
+        <v>4.523438400000001</v>
       </c>
       <c r="Q80">
-        <v>8.789433855999999</v>
+        <v>7.653438400000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4760063518554048</v>
+        <v>0.4948032914988058</v>
       </c>
       <c r="T80">
-        <v>2.631088493829808</v>
+        <v>2.746048236757054</v>
       </c>
       <c r="U80">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V80">
         <v>0.29</v>
       </c>
       <c r="W80">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.009123624073144</v>
+        <v>1.670709214482428</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1543896912147492</v>
+        <v>0.1542159850213093</v>
       </c>
       <c r="C81">
-        <v>53.31650873812352</v>
+        <v>52.23329170647071</v>
       </c>
       <c r="D81">
-        <v>157.7705087381235</v>
+        <v>158.0232917064707</v>
       </c>
       <c r="E81">
-        <v>65.14400000000001</v>
+        <v>66.47999999999999</v>
       </c>
       <c r="F81">
-        <v>105.544</v>
+        <v>106.88</v>
       </c>
       <c r="G81">
         <v>1.09</v>
@@ -8054,28 +8054,28 @@
         <v>15.87</v>
       </c>
       <c r="M81">
-        <v>9.498959999999999</v>
+        <v>9.619199999999999</v>
       </c>
       <c r="N81">
-        <v>6.371040000000001</v>
+        <v>6.2508</v>
       </c>
       <c r="O81">
-        <v>1.8476016</v>
+        <v>1.812732</v>
       </c>
       <c r="P81">
-        <v>4.523438400000001</v>
+        <v>4.438068</v>
       </c>
       <c r="Q81">
-        <v>7.653438400000002</v>
+        <v>7.568068000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4948032914988058</v>
+        <v>0.5154799251065468</v>
       </c>
       <c r="T81">
-        <v>2.746048236757054</v>
+        <v>2.872503953977025</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.670709214482428</v>
+        <v>1.649825349301397</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1542159850213093</v>
+        <v>0.1540422788278695</v>
       </c>
       <c r="C82">
-        <v>52.23329170647071</v>
+        <v>51.15088600228935</v>
       </c>
       <c r="D82">
-        <v>158.0232917064707</v>
+        <v>158.2768860022894</v>
       </c>
       <c r="E82">
-        <v>66.47999999999999</v>
+        <v>67.816</v>
       </c>
       <c r="F82">
-        <v>106.88</v>
+        <v>108.216</v>
       </c>
       <c r="G82">
         <v>1.09</v>
@@ -8136,28 +8136,28 @@
         <v>15.87</v>
       </c>
       <c r="M82">
-        <v>9.619199999999999</v>
+        <v>9.73944</v>
       </c>
       <c r="N82">
-        <v>6.2508</v>
+        <v>6.130559999999999</v>
       </c>
       <c r="O82">
-        <v>1.812732</v>
+        <v>1.7778624</v>
       </c>
       <c r="P82">
-        <v>4.438068</v>
+        <v>4.352697599999999</v>
       </c>
       <c r="Q82">
-        <v>7.568068000000001</v>
+        <v>7.4826976</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5154799251065468</v>
+        <v>0.5383330464624713</v>
       </c>
       <c r="T82">
-        <v>2.872503953977025</v>
+        <v>3.012270799325414</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.649825349301397</v>
+        <v>1.629457135112491</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1540422788278695</v>
+        <v>0.1538685726344297</v>
       </c>
       <c r="C83">
-        <v>51.15088600228935</v>
+        <v>50.06929553789023</v>
       </c>
       <c r="D83">
-        <v>158.2768860022894</v>
+        <v>158.5312955378902</v>
       </c>
       <c r="E83">
-        <v>67.816</v>
+        <v>69.15200000000002</v>
       </c>
       <c r="F83">
-        <v>108.216</v>
+        <v>109.552</v>
       </c>
       <c r="G83">
         <v>1.09</v>
@@ -8218,28 +8218,28 @@
         <v>15.87</v>
       </c>
       <c r="M83">
-        <v>9.73944</v>
+        <v>9.859680000000001</v>
       </c>
       <c r="N83">
-        <v>6.130559999999999</v>
+        <v>6.010319999999998</v>
       </c>
       <c r="O83">
-        <v>1.7778624</v>
+        <v>1.742992799999999</v>
       </c>
       <c r="P83">
-        <v>4.352697599999999</v>
+        <v>4.267327199999999</v>
       </c>
       <c r="Q83">
-        <v>7.4826976</v>
+        <v>7.397327199999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5383330464624713</v>
+        <v>0.5637254035246094</v>
       </c>
       <c r="T83">
-        <v>3.012270799325414</v>
+        <v>3.167567294156957</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.629457135112491</v>
+        <v>1.609585706635509</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1538685726344297</v>
+        <v>0.1536948664409898</v>
       </c>
       <c r="C84">
-        <v>50.06929553789023</v>
+        <v>48.98852425077834</v>
       </c>
       <c r="D84">
-        <v>158.5312955378902</v>
+        <v>158.7865242507783</v>
       </c>
       <c r="E84">
-        <v>69.15200000000002</v>
+        <v>70.488</v>
       </c>
       <c r="F84">
-        <v>109.552</v>
+        <v>110.888</v>
       </c>
       <c r="G84">
         <v>1.09</v>
@@ -8300,28 +8300,28 @@
         <v>15.87</v>
       </c>
       <c r="M84">
-        <v>9.859680000000001</v>
+        <v>9.97992</v>
       </c>
       <c r="N84">
-        <v>6.010319999999998</v>
+        <v>5.890079999999999</v>
       </c>
       <c r="O84">
-        <v>1.742992799999999</v>
+        <v>1.7081232</v>
       </c>
       <c r="P84">
-        <v>4.267327199999999</v>
+        <v>4.1819568</v>
       </c>
       <c r="Q84">
-        <v>7.397327199999999</v>
+        <v>7.311956800000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5637254035246094</v>
+        <v>0.5921050967117051</v>
       </c>
       <c r="T84">
-        <v>3.167567294156957</v>
+        <v>3.341133964851035</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.609585706635509</v>
+        <v>1.590193107760383</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1536948664409898</v>
+        <v>0.15352116024755</v>
       </c>
       <c r="C85">
-        <v>48.98852425077834</v>
+        <v>47.90857610385679</v>
       </c>
       <c r="D85">
-        <v>158.7865242507783</v>
+        <v>159.0425761038568</v>
       </c>
       <c r="E85">
-        <v>70.488</v>
+        <v>71.82400000000001</v>
       </c>
       <c r="F85">
-        <v>110.888</v>
+        <v>112.224</v>
       </c>
       <c r="G85">
         <v>1.09</v>
@@ -8382,28 +8382,28 @@
         <v>15.87</v>
       </c>
       <c r="M85">
-        <v>9.97992</v>
+        <v>10.10016</v>
       </c>
       <c r="N85">
-        <v>5.890079999999999</v>
+        <v>5.769839999999999</v>
       </c>
       <c r="O85">
-        <v>1.7081232</v>
+        <v>1.6732536</v>
       </c>
       <c r="P85">
-        <v>4.1819568</v>
+        <v>4.096586399999999</v>
       </c>
       <c r="Q85">
-        <v>7.311956800000001</v>
+        <v>7.2265864</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5921050967117051</v>
+        <v>0.6240322515471878</v>
       </c>
       <c r="T85">
-        <v>3.341133964851035</v>
+        <v>3.536396469381873</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.590193107760383</v>
+        <v>1.571262237429902</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.15352116024755</v>
+        <v>0.1533474540541102</v>
       </c>
       <c r="C86">
-        <v>47.9085761038568</v>
+        <v>46.82945508563138</v>
       </c>
       <c r="D86">
-        <v>159.0425761038568</v>
+        <v>159.2994550856314</v>
       </c>
       <c r="E86">
-        <v>71.82399999999998</v>
+        <v>73.16</v>
       </c>
       <c r="F86">
-        <v>112.224</v>
+        <v>113.56</v>
       </c>
       <c r="G86">
         <v>1.09</v>
@@ -8464,28 +8464,28 @@
         <v>15.87</v>
       </c>
       <c r="M86">
-        <v>10.10016</v>
+        <v>10.2204</v>
       </c>
       <c r="N86">
-        <v>5.76984</v>
+        <v>5.649600000000001</v>
       </c>
       <c r="O86">
-        <v>1.6732536</v>
+        <v>1.638384</v>
       </c>
       <c r="P86">
-        <v>4.096586400000001</v>
+        <v>4.011216000000001</v>
       </c>
       <c r="Q86">
-        <v>7.226586400000001</v>
+        <v>7.141216000000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6240322515471873</v>
+        <v>0.6602163603607343</v>
       </c>
       <c r="T86">
-        <v>3.53639646938187</v>
+        <v>3.757693974516819</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.571262237429902</v>
+        <v>1.552776799342492</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1533474540541102</v>
+        <v>0.1531737478606703</v>
       </c>
       <c r="C87">
-        <v>46.82945508563138</v>
+        <v>45.75116521041787</v>
       </c>
       <c r="D87">
-        <v>159.2994550856314</v>
+        <v>159.5571652104178</v>
       </c>
       <c r="E87">
-        <v>73.16</v>
+        <v>74.49599999999998</v>
       </c>
       <c r="F87">
-        <v>113.56</v>
+        <v>114.896</v>
       </c>
       <c r="G87">
         <v>1.09</v>
@@ -8546,28 +8546,28 @@
         <v>15.87</v>
       </c>
       <c r="M87">
-        <v>10.2204</v>
+        <v>10.34064</v>
       </c>
       <c r="N87">
-        <v>5.649600000000001</v>
+        <v>5.52936</v>
       </c>
       <c r="O87">
-        <v>1.638384</v>
+        <v>1.6035144</v>
       </c>
       <c r="P87">
-        <v>4.011216000000001</v>
+        <v>3.925845600000001</v>
       </c>
       <c r="Q87">
-        <v>7.141216000000002</v>
+        <v>7.055845600000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6602163603607343</v>
+        <v>0.7015696275762165</v>
       </c>
       <c r="T87">
-        <v>3.757693974516819</v>
+        <v>4.010605408956761</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.552776799342492</v>
+        <v>1.534721255164091</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1531737478606703</v>
+        <v>0.1530000416672305</v>
       </c>
       <c r="C88">
-        <v>45.75116521041787</v>
+        <v>44.67371051855116</v>
       </c>
       <c r="D88">
-        <v>159.5571652104178</v>
+        <v>159.8157105185512</v>
       </c>
       <c r="E88">
-        <v>74.49599999999998</v>
+        <v>75.83199999999999</v>
       </c>
       <c r="F88">
-        <v>114.896</v>
+        <v>116.232</v>
       </c>
       <c r="G88">
         <v>1.09</v>
@@ -8628,28 +8628,28 @@
         <v>15.87</v>
       </c>
       <c r="M88">
-        <v>10.34064</v>
+        <v>10.46088</v>
       </c>
       <c r="N88">
-        <v>5.52936</v>
+        <v>5.40912</v>
       </c>
       <c r="O88">
-        <v>1.6035144</v>
+        <v>1.5686448</v>
       </c>
       <c r="P88">
-        <v>3.925845600000001</v>
+        <v>3.8404752</v>
       </c>
       <c r="Q88">
-        <v>7.055845600000001</v>
+        <v>6.970475200000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7015696275762165</v>
+        <v>0.7492849359017729</v>
       </c>
       <c r="T88">
-        <v>4.010605408956761</v>
+        <v>4.302426294849001</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.534721255164091</v>
+        <v>1.517080780966802</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1530000416672305</v>
+        <v>0.1938420594896159</v>
       </c>
       <c r="C89">
-        <v>44.67371051855116</v>
+        <v>-0.7524360235786389</v>
       </c>
       <c r="D89">
-        <v>159.8157105185512</v>
+        <v>115.7255639764214</v>
       </c>
       <c r="E89">
-        <v>75.83199999999999</v>
+        <v>77.16800000000001</v>
       </c>
       <c r="F89">
-        <v>116.232</v>
+        <v>117.568</v>
       </c>
       <c r="G89">
         <v>1.09</v>
@@ -8710,45 +8710,45 @@
         <v>15.87</v>
       </c>
       <c r="M89">
-        <v>10.46088</v>
+        <v>17.2589824</v>
       </c>
       <c r="N89">
-        <v>5.40912</v>
+        <v>-1.388982400000002</v>
       </c>
       <c r="O89">
-        <v>1.5686448</v>
+        <v>-0.4028048960000004</v>
       </c>
       <c r="P89">
-        <v>3.8404752</v>
+        <v>-0.9861775040000011</v>
       </c>
       <c r="Q89">
-        <v>6.970475200000001</v>
+        <v>2.143822495999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7492849359017729</v>
+        <v>0.8258867731919093</v>
       </c>
       <c r="T89">
-        <v>4.302426294849001</v>
+        <v>4.770913595957103</v>
       </c>
       <c r="U89">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.29</v>
+        <v>0.2666611445179989</v>
       </c>
       <c r="W89">
-        <v>0.0639</v>
+        <v>0.1076541439847578</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y89">
-        <v>1.517080780966802</v>
+        <v>0.9195211879930997</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1938420594896159</v>
+        <v>0.194852059489616</v>
       </c>
       <c r="C90">
-        <v>-0.7524360235786389</v>
+        <v>-2.872610492662915</v>
       </c>
       <c r="D90">
-        <v>115.7255639764214</v>
+        <v>114.9413895073371</v>
       </c>
       <c r="E90">
-        <v>77.16800000000001</v>
+        <v>78.50399999999999</v>
       </c>
       <c r="F90">
-        <v>117.568</v>
+        <v>118.904</v>
       </c>
       <c r="G90">
         <v>1.09</v>
@@ -8792,37 +8792,37 @@
         <v>15.87</v>
       </c>
       <c r="M90">
-        <v>17.2589824</v>
+        <v>17.4551072</v>
       </c>
       <c r="N90">
-        <v>-1.388982400000002</v>
+        <v>-1.585107200000001</v>
       </c>
       <c r="O90">
-        <v>-0.4028048960000004</v>
+        <v>-0.4596810880000003</v>
       </c>
       <c r="P90">
-        <v>-0.9861775040000011</v>
+        <v>-1.125426112000001</v>
       </c>
       <c r="Q90">
-        <v>2.143822495999999</v>
+        <v>2.004573888</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8258867731919093</v>
+        <v>0.8968037525729921</v>
       </c>
       <c r="T90">
-        <v>4.770913595957103</v>
+        <v>5.204633013771385</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2666611445179989</v>
+        <v>0.2636649518829652</v>
       </c>
       <c r="W90">
-        <v>0.1076541439847578</v>
+        <v>0.1080939850635807</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9195211879930997</v>
+        <v>0.9091894892516041</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.194852059489616</v>
+        <v>0.1958620594896159</v>
       </c>
       <c r="C91">
-        <v>-2.872610492662915</v>
+        <v>-4.982229112834148</v>
       </c>
       <c r="D91">
-        <v>114.9413895073371</v>
+        <v>114.1677708871658</v>
       </c>
       <c r="E91">
-        <v>78.50399999999999</v>
+        <v>79.84</v>
       </c>
       <c r="F91">
-        <v>118.904</v>
+        <v>120.24</v>
       </c>
       <c r="G91">
         <v>1.09</v>
@@ -8874,37 +8874,37 @@
         <v>15.87</v>
       </c>
       <c r="M91">
-        <v>17.4551072</v>
+        <v>17.651232</v>
       </c>
       <c r="N91">
-        <v>-1.585107200000001</v>
+        <v>-1.781232000000001</v>
       </c>
       <c r="O91">
-        <v>-0.4596810880000003</v>
+        <v>-0.5165572800000002</v>
       </c>
       <c r="P91">
-        <v>-1.125426112000001</v>
+        <v>-1.264674720000001</v>
       </c>
       <c r="Q91">
-        <v>2.004573888</v>
+        <v>1.86532528</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8968037525729921</v>
+        <v>0.9819041278302912</v>
       </c>
       <c r="T91">
-        <v>5.204633013771385</v>
+        <v>5.725096315148524</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2636649518829652</v>
+        <v>0.2607353413064878</v>
       </c>
       <c r="W91">
-        <v>0.1080939850635807</v>
+        <v>0.1085240518962076</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.9091894892516041</v>
+        <v>0.8990873838154753</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1958620594896159</v>
+        <v>0.1968720594896159</v>
       </c>
       <c r="C92">
-        <v>-4.982229112834148</v>
+        <v>-7.081503599099847</v>
       </c>
       <c r="D92">
-        <v>114.1677708871658</v>
+        <v>113.4044964009001</v>
       </c>
       <c r="E92">
-        <v>79.84</v>
+        <v>81.17599999999999</v>
       </c>
       <c r="F92">
-        <v>120.24</v>
+        <v>121.576</v>
       </c>
       <c r="G92">
         <v>1.09</v>
@@ -8956,37 +8956,37 @@
         <v>15.87</v>
       </c>
       <c r="M92">
-        <v>17.651232</v>
+        <v>17.8473568</v>
       </c>
       <c r="N92">
-        <v>-1.781232000000001</v>
+        <v>-1.977356800000001</v>
       </c>
       <c r="O92">
-        <v>-0.5165572800000002</v>
+        <v>-0.5734334720000002</v>
       </c>
       <c r="P92">
-        <v>-1.264674720000001</v>
+        <v>-1.403923328000001</v>
       </c>
       <c r="Q92">
-        <v>1.86532528</v>
+        <v>1.726076672</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9819041278302912</v>
+        <v>1.085915697589213</v>
       </c>
       <c r="T92">
-        <v>5.725096315148524</v>
+        <v>6.361218127942806</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2607353413064878</v>
+        <v>0.2578701177756473</v>
       </c>
       <c r="W92">
-        <v>0.1085240518962076</v>
+        <v>0.108944666710535</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8990873838154753</v>
+        <v>0.8892073026746459</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1968720594896159</v>
+        <v>0.197882059489616</v>
       </c>
       <c r="C93">
-        <v>-7.081503599099847</v>
+        <v>-9.170640042341745</v>
       </c>
       <c r="D93">
-        <v>113.4044964009001</v>
+        <v>112.6513599576583</v>
       </c>
       <c r="E93">
-        <v>81.17599999999999</v>
+        <v>82.512</v>
       </c>
       <c r="F93">
-        <v>121.576</v>
+        <v>122.912</v>
       </c>
       <c r="G93">
         <v>1.09</v>
@@ -9038,37 +9038,37 @@
         <v>15.87</v>
       </c>
       <c r="M93">
-        <v>17.8473568</v>
+        <v>18.0434816</v>
       </c>
       <c r="N93">
-        <v>-1.977356800000001</v>
+        <v>-2.173481600000004</v>
       </c>
       <c r="O93">
-        <v>-0.5734334720000002</v>
+        <v>-0.6303096640000011</v>
       </c>
       <c r="P93">
-        <v>-1.403923328000001</v>
+        <v>-1.543171936000003</v>
       </c>
       <c r="Q93">
-        <v>1.726076672</v>
+        <v>1.586828063999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.085915697589213</v>
+        <v>1.215930159787865</v>
       </c>
       <c r="T93">
-        <v>6.361218127942806</v>
+        <v>7.156370393935658</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2578701177756473</v>
+        <v>0.2550671817128685</v>
       </c>
       <c r="W93">
-        <v>0.108944666710535</v>
+        <v>0.1093561377245509</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8892073026746459</v>
+        <v>0.879542005906443</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.197882059489616</v>
+        <v>0.198892059489616</v>
       </c>
       <c r="C94">
-        <v>-9.170640042341745</v>
+        <v>-11.24983909483706</v>
       </c>
       <c r="D94">
-        <v>112.6513599576583</v>
+        <v>111.9081609051629</v>
       </c>
       <c r="E94">
-        <v>82.512</v>
+        <v>83.84800000000001</v>
       </c>
       <c r="F94">
-        <v>122.912</v>
+        <v>124.248</v>
       </c>
       <c r="G94">
         <v>1.09</v>
@@ -9120,37 +9120,37 @@
         <v>15.87</v>
       </c>
       <c r="M94">
-        <v>18.0434816</v>
+        <v>18.2396064</v>
       </c>
       <c r="N94">
-        <v>-2.173481600000004</v>
+        <v>-2.369606400000004</v>
       </c>
       <c r="O94">
-        <v>-0.6303096640000011</v>
+        <v>-0.687185856000001</v>
       </c>
       <c r="P94">
-        <v>-1.543171936000003</v>
+        <v>-1.682420544000003</v>
       </c>
       <c r="Q94">
-        <v>1.586828063999998</v>
+        <v>1.447579455999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.215930159787865</v>
+        <v>1.383091611186132</v>
       </c>
       <c r="T94">
-        <v>7.156370393935658</v>
+        <v>8.178709021640755</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2550671817128685</v>
+        <v>0.2523245238449882</v>
       </c>
       <c r="W94">
-        <v>0.1093561377245509</v>
+        <v>0.1097587598995557</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.879542005906443</v>
+        <v>0.8700845649827178</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.198892059489616</v>
+        <v>0.199902059489616</v>
       </c>
       <c r="C95">
-        <v>-11.24983909483706</v>
+        <v>-13.3192961484842</v>
       </c>
       <c r="D95">
-        <v>111.9081609051629</v>
+        <v>111.1747038515158</v>
       </c>
       <c r="E95">
-        <v>83.84800000000001</v>
+        <v>85.184</v>
       </c>
       <c r="F95">
-        <v>124.248</v>
+        <v>125.584</v>
       </c>
       <c r="G95">
         <v>1.09</v>
@@ -9202,37 +9202,37 @@
         <v>15.87</v>
       </c>
       <c r="M95">
-        <v>18.2396064</v>
+        <v>18.4357312</v>
       </c>
       <c r="N95">
-        <v>-2.369606400000004</v>
+        <v>-2.565731200000004</v>
       </c>
       <c r="O95">
-        <v>-0.687185856000001</v>
+        <v>-0.744062048000001</v>
       </c>
       <c r="P95">
-        <v>-1.682420544000003</v>
+        <v>-1.821669152000003</v>
       </c>
       <c r="Q95">
-        <v>1.447579455999998</v>
+        <v>1.308330847999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.383091611186132</v>
+        <v>1.60597354638382</v>
       </c>
       <c r="T95">
-        <v>8.178709021640755</v>
+        <v>9.541827191914214</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2523245238449882</v>
+        <v>0.2496402203998287</v>
       </c>
       <c r="W95">
-        <v>0.1097587598995557</v>
+        <v>0.1101528156453052</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8700845649827178</v>
+        <v>0.860828346206306</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.199902059489616</v>
+        <v>0.200912059489616</v>
       </c>
       <c r="C96">
-        <v>-13.3192961484842</v>
+        <v>-15.37920150606571</v>
       </c>
       <c r="D96">
-        <v>111.1747038515158</v>
+        <v>110.4507984939343</v>
       </c>
       <c r="E96">
-        <v>85.184</v>
+        <v>86.52000000000001</v>
       </c>
       <c r="F96">
-        <v>125.584</v>
+        <v>126.92</v>
       </c>
       <c r="G96">
         <v>1.09</v>
@@ -9284,37 +9284,37 @@
         <v>15.87</v>
       </c>
       <c r="M96">
-        <v>18.4357312</v>
+        <v>18.631856</v>
       </c>
       <c r="N96">
-        <v>-2.565731200000004</v>
+        <v>-2.761856000000003</v>
       </c>
       <c r="O96">
-        <v>-0.744062048000001</v>
+        <v>-0.8009382400000009</v>
       </c>
       <c r="P96">
-        <v>-1.821669152000003</v>
+        <v>-1.960917760000003</v>
       </c>
       <c r="Q96">
-        <v>1.308330847999998</v>
+        <v>1.169082239999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.60597354638382</v>
+        <v>1.918008255660585</v>
       </c>
       <c r="T96">
-        <v>9.541827191914214</v>
+        <v>11.45019263029706</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2496402203998287</v>
+        <v>0.2470124286061463</v>
       </c>
       <c r="W96">
-        <v>0.1101528156453052</v>
+        <v>0.1105385754806177</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.860828346206306</v>
+        <v>0.851766995193608</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.200912059489616</v>
+        <v>0.2019220594896159</v>
       </c>
       <c r="C97">
-        <v>-15.37920150606571</v>
+        <v>-17.42974054586288</v>
       </c>
       <c r="D97">
-        <v>110.4507984939343</v>
+        <v>109.7362594541371</v>
       </c>
       <c r="E97">
-        <v>86.52000000000001</v>
+        <v>87.85599999999999</v>
       </c>
       <c r="F97">
-        <v>126.92</v>
+        <v>128.256</v>
       </c>
       <c r="G97">
         <v>1.09</v>
@@ -9366,37 +9366,37 @@
         <v>15.87</v>
       </c>
       <c r="M97">
-        <v>18.631856</v>
+        <v>18.8279808</v>
       </c>
       <c r="N97">
-        <v>-2.761856000000003</v>
+        <v>-2.957980800000003</v>
       </c>
       <c r="O97">
-        <v>-0.8009382400000009</v>
+        <v>-0.8578144320000008</v>
       </c>
       <c r="P97">
-        <v>-1.960917760000003</v>
+        <v>-2.100166368000002</v>
       </c>
       <c r="Q97">
-        <v>1.169082239999998</v>
+        <v>1.029833631999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.918008255660585</v>
+        <v>2.386060319575732</v>
       </c>
       <c r="T97">
-        <v>11.45019263029706</v>
+        <v>14.31274078787133</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2470124286061463</v>
+        <v>0.2444393824748323</v>
       </c>
       <c r="W97">
-        <v>0.1105385754806177</v>
+        <v>0.1109162986526946</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.851766995193608</v>
+        <v>0.842894422327008</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2019220594896159</v>
+        <v>0.202932059489616</v>
       </c>
       <c r="C98">
-        <v>-17.42974054586288</v>
+        <v>-19.47109387992265</v>
       </c>
       <c r="D98">
-        <v>109.7362594541371</v>
+        <v>109.0309061200773</v>
       </c>
       <c r="E98">
-        <v>87.85599999999999</v>
+        <v>89.19199999999998</v>
       </c>
       <c r="F98">
-        <v>128.256</v>
+        <v>129.592</v>
       </c>
       <c r="G98">
         <v>1.09</v>
@@ -9448,37 +9448,37 @@
         <v>15.87</v>
       </c>
       <c r="M98">
-        <v>18.8279808</v>
+        <v>19.0241056</v>
       </c>
       <c r="N98">
-        <v>-2.957980800000003</v>
+        <v>-3.154105599999999</v>
       </c>
       <c r="O98">
-        <v>-0.8578144320000008</v>
+        <v>-0.9146906239999998</v>
       </c>
       <c r="P98">
-        <v>-2.100166368000002</v>
+        <v>-2.239414976</v>
       </c>
       <c r="Q98">
-        <v>1.029833631999999</v>
+        <v>0.8905850240000013</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.386060319575726</v>
+        <v>3.166147092767635</v>
       </c>
       <c r="T98">
-        <v>14.3127407878713</v>
+        <v>19.0836543838284</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2444393824748323</v>
+        <v>0.2419193888410712</v>
       </c>
       <c r="W98">
-        <v>0.1109162986526946</v>
+        <v>0.1112862337181308</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.842894422327008</v>
+        <v>0.834204789107142</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.202932059489616</v>
+        <v>0.203942059489616</v>
       </c>
       <c r="C99">
-        <v>-19.47109387992265</v>
+        <v>-21.50343750625889</v>
       </c>
       <c r="D99">
-        <v>109.0309061200773</v>
+        <v>108.3345624937411</v>
       </c>
       <c r="E99">
-        <v>89.19199999999998</v>
+        <v>90.52799999999999</v>
       </c>
       <c r="F99">
-        <v>129.592</v>
+        <v>130.928</v>
       </c>
       <c r="G99">
         <v>1.09</v>
@@ -9530,37 +9530,37 @@
         <v>15.87</v>
       </c>
       <c r="M99">
-        <v>19.0241056</v>
+        <v>19.2202304</v>
       </c>
       <c r="N99">
-        <v>-3.154105599999999</v>
+        <v>-3.350230400000003</v>
       </c>
       <c r="O99">
-        <v>-0.9146906239999998</v>
+        <v>-0.9715668160000007</v>
       </c>
       <c r="P99">
-        <v>-2.239414976</v>
+        <v>-2.378663584000002</v>
       </c>
       <c r="Q99">
-        <v>0.8905850240000013</v>
+        <v>0.7513364159999987</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.166147092767635</v>
+        <v>4.726320639151451</v>
       </c>
       <c r="T99">
-        <v>19.0836543838284</v>
+        <v>28.62548157574259</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2419193888410712</v>
+        <v>0.2394508236488153</v>
       </c>
       <c r="W99">
-        <v>0.1112862337181308</v>
+        <v>0.1116486190883539</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.834204789107142</v>
+        <v>0.8256924953407425</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.203942059489616</v>
+        <v>0.2049520594896159</v>
       </c>
       <c r="C100">
-        <v>-21.50343750625889</v>
+        <v>-23.52694295525882</v>
       </c>
       <c r="D100">
-        <v>108.3345624937411</v>
+        <v>107.6470570447412</v>
       </c>
       <c r="E100">
-        <v>90.52799999999999</v>
+        <v>91.86399999999998</v>
       </c>
       <c r="F100">
-        <v>130.928</v>
+        <v>132.264</v>
       </c>
       <c r="G100">
         <v>1.09</v>
@@ -9612,37 +9612,37 @@
         <v>15.87</v>
       </c>
       <c r="M100">
-        <v>19.2202304</v>
+        <v>19.4163552</v>
       </c>
       <c r="N100">
-        <v>-3.350230400000003</v>
+        <v>-3.546355199999999</v>
       </c>
       <c r="O100">
-        <v>-0.9715668160000007</v>
+        <v>-1.028443008</v>
       </c>
       <c r="P100">
-        <v>-2.378663584000002</v>
+        <v>-2.517912191999999</v>
       </c>
       <c r="Q100">
-        <v>0.7513364159999987</v>
+        <v>0.6120878080000014</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.726320639151451</v>
+        <v>9.406841278302903</v>
       </c>
       <c r="T100">
-        <v>28.62548157574259</v>
+        <v>57.25096315148518</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2394508236488153</v>
+        <v>0.2370321284604435</v>
       </c>
       <c r="W100">
-        <v>0.1116486190883539</v>
+        <v>0.1120036835420069</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8256924953407425</v>
+        <v>0.8173521671049776</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2049520594896159</v>
-      </c>
-      <c r="C101">
-        <v>-23.52694295525882</v>
-      </c>
-      <c r="D101">
-        <v>107.6470570447412</v>
-      </c>
-      <c r="E101">
-        <v>91.86399999999998</v>
-      </c>
-      <c r="F101">
-        <v>132.264</v>
-      </c>
-      <c r="G101">
-        <v>1.09</v>
-      </c>
-      <c r="H101">
-        <v>93.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>19</v>
-      </c>
-      <c r="K101">
-        <v>3.130000000000001</v>
-      </c>
-      <c r="L101">
-        <v>15.87</v>
-      </c>
-      <c r="M101">
-        <v>19.4163552</v>
-      </c>
-      <c r="N101">
-        <v>-3.546355199999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.028443008</v>
-      </c>
-      <c r="P101">
-        <v>-2.517912191999999</v>
-      </c>
-      <c r="Q101">
-        <v>0.6120878080000014</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.406841278302903</v>
-      </c>
-      <c r="T101">
-        <v>57.25096315148518</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2370321284604435</v>
-      </c>
-      <c r="W101">
-        <v>0.1120036835420069</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8173521671049776</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
